--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6686</v>
+        <v>6793</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2397</v>
+        <v>2436</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6686</v>
+        <v>6793</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2397</v>
+        <v>2436</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6793</v>
+        <v>6924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2436</v>
+        <v>2482</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1821,43 +1821,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>528</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1872,36 +1872,82 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>12</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>225</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
@@ -1918,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,7 +2088,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2207,41 +2253,87 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024.02.25 19:30-02.25 21:10</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
@@ -2336,7 +2428,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2368,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2446,7 +2538,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2492,7 +2584,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2630,7 +2722,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2676,7 +2768,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2768,7 +2860,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2814,7 +2906,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6793</v>
+        <v>6924</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2860,7 +2952,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2906,7 +2998,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2952,7 +3044,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2998,7 +3090,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3044,7 +3136,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3090,7 +3182,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3136,7 +3228,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3182,7 +3274,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3228,7 +3320,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3320,7 +3412,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2436</v>
+        <v>2482</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3366,7 +3458,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3458,7 +3550,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3504,7 +3596,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3531,30 +3623,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -3562,12 +3654,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3582,25 +3674,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>407</v>
+        <v>35</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -3608,12 +3700,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,43 +3715,43 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>54</v>
+        <v>412</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3766,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3688,24 +3780,24 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3715,30 +3807,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -3746,12 +3838,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3766,25 +3858,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -3792,12 +3884,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3812,38 +3904,38 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3858,38 +3950,38 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,25 +3996,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -3930,12 +4022,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,25 +4042,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -3976,12 +4068,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,30 +4083,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·筑梦城堡巡回展降临之章</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>302</v>
+        <v>15</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -4022,12 +4114,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -4037,30 +4129,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>336</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -4068,12 +4160,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4083,43 +4175,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>528</t>
         </is>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4129,41 +4221,133 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>12</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>225</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F41" t="n">
         <v>5</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -625,43 +625,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·心动次元动漫游戏展</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.01 10:30-02.01 16:30</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>7065</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/RPFhOk511704875616895.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -676,38 +676,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6924</v>
+        <v>2718</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -722,25 +722,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2720</v>
+        <v>915</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -748,12 +748,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -763,30 +763,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>912</v>
+        <v>271</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -794,12 +794,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,25 +814,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>266</v>
+        <v>760</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -840,12 +840,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,43 +855,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>751</v>
+        <v>538</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,43 +901,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>522</v>
+        <v>11</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -947,43 +947,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -998,38 +998,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·心动次元动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XOt6GoR71706165982147.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2482</v>
+        <v>2825</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1223,43 +1223,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -1274,25 +1274,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>734</v>
+        <v>192</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,43 +1315,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>734</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -1366,25 +1366,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>412</v>
+        <v>36</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -1407,43 +1407,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1472,24 +1472,24 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,30 +1499,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,25 +1596,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1688,38 +1688,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1748,11 +1748,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1775,30 +1775,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1821,43 +1821,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·筑梦城堡巡回展降临之章</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1867,43 +1867,43 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1913,41 +1913,179 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>杭州·AD02动漫展</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024.03.23 10:00-03.24 17:00</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>359</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.03.24 10:00-03.24 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>2024-04-04</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F36" t="n">
         <v>225</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
@@ -2180,7 +2318,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2226,7 +2364,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2318,7 +2456,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2428,7 +2566,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2460,7 +2598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2538,7 +2676,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2584,7 +2722,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2722,7 +2860,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2841,43 +2979,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·心动次元动漫游戏展</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.01 10:30-02.01 16:30</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>7065</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/RPFhOk511704875616895.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -2892,38 +3030,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6924</v>
+        <v>2718</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -2938,25 +3076,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2720</v>
+        <v>915</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -2964,12 +3102,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -2979,30 +3117,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>912</v>
+        <v>271</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -3010,12 +3148,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -3030,25 +3168,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>266</v>
+        <v>760</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -3056,12 +3194,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -3071,43 +3209,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>751</v>
+        <v>538</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -3117,43 +3255,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.07 10:00-02.07 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>522</v>
+        <v>11</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3163,43 +3301,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -3214,38 +3352,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·心动次元动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/XOt6GoR71706165982147.jpeg</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3412,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3320,7 +3458,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3366,7 +3504,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3412,7 +3550,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2482</v>
+        <v>2825</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3458,7 +3596,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3485,30 +3623,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -3516,12 +3654,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3536,38 +3674,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>185</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3582,25 +3720,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>734</v>
+        <v>192</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -3608,12 +3746,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,43 +3761,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3669,30 +3807,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -3700,12 +3838,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3720,25 +3858,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>412</v>
+        <v>36</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -3746,12 +3884,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,43 +3899,43 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3950,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3826,24 +3964,24 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3853,30 +3991,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -3884,12 +4022,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,17 +4042,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -3922,7 +4060,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -3930,12 +4068,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,25 +4088,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -3976,12 +4114,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3996,12 +4134,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4010,11 +4148,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -4022,12 +4160,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -4042,38 +4180,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -4088,12 +4226,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4102,11 +4240,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -4114,12 +4252,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -4129,30 +4267,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>336</v>
+        <v>8</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -4160,12 +4298,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4175,43 +4313,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·筑梦城堡巡回展降临之章</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -4221,43 +4359,43 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4267,30 +4405,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>225</v>
+        <v>359</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -4298,12 +4436,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4313,41 +4451,179 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.03.24 10:00-03.24 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>15</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>225</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -506,22 +501,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>990</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
+        <v>1015</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79906</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79906</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/fsCnC2E81702888590146.jpeg</t>
         </is>
@@ -533,43 +523,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·VOCALOID ONLY（取消）</t>
+          <t>杭州·文豪野犬舞会ONLY:横滨晚宴（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>九环路7号 杭州鑫牛大厦</t>
+          <t>九龙大道227号 七里香溪别墅园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.01.28 10:00-01.28 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>118</v>
+        <v>845</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H3" t="b">
-        <v>1</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77627</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80374</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/2Znkbtbv1704250050863.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/n3gFbUkJ1698202692701.jpeg</t>
         </is>
       </c>
     </row>
@@ -579,43 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·文豪野犬舞会ONLY:横滨晚宴（取消）</t>
+          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九龙大道227号 七里香溪别墅园</t>
+          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>845</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>55</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77627</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/n3gFbUkJ1698202692701.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
         </is>
       </c>
     </row>
@@ -644,22 +626,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7065</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>7474</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
@@ -690,22 +667,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H6" t="b">
-        <v>0</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
@@ -736,22 +710,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>已售罄</t>
         </is>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
@@ -782,22 +753,17 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>271</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>284</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
@@ -828,22 +794,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>760</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>780</v>
+      </c>
+      <c r="G9" t="n">
+        <v>68</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
@@ -874,22 +835,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>538</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
+        <v>574</v>
+      </c>
+      <c r="G10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
@@ -901,43 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="G11" t="n">
+        <v>88</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -952,38 +903,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="G12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -993,43 +939,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·心动次元动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>374</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XOt6GoR71706165982147.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -1044,38 +987,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>370</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>852</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -1085,43 +1023,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>834</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>2993</v>
+      </c>
+      <c r="G15" t="n">
+        <v>65</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1069,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1150,24 +1083,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2825</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
+        <v>174</v>
+      </c>
+      <c r="G16" t="n">
+        <v>138</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -1177,43 +1105,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>139</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="G17" t="n">
+        <v>59</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -1223,43 +1146,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>697</v>
+      </c>
+      <c r="G18" t="n">
+        <v>65</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1274,38 +1192,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>192</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
+        <v>745</v>
+      </c>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,43 +1228,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>734</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="G20" t="n">
+        <v>70</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -1366,38 +1274,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>438</v>
+      </c>
+      <c r="G21" t="n">
+        <v>89</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -1407,43 +1310,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>419</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1472,22 +1370,17 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>119</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
+        <v>184</v>
+      </c>
+      <c r="G23" t="n">
+        <v>70</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
@@ -1518,22 +1411,17 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>178</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>202</v>
+      </c>
+      <c r="G24" t="n">
+        <v>65</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
@@ -1564,22 +1452,17 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
@@ -1610,22 +1493,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>148</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>1</v>
+        <v>236</v>
+      </c>
+      <c r="G26" t="n">
+        <v>218</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
@@ -1656,22 +1534,17 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>111</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="G27" t="n">
+        <v>88</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
@@ -1702,22 +1575,17 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>62</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>1</v>
+        <v>86</v>
+      </c>
+      <c r="G28" t="n">
+        <v>68</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
@@ -1748,22 +1616,17 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>167</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
@@ -1794,22 +1657,17 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
+        <v>78</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
@@ -1826,7 +1684,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1840,22 +1698,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
@@ -1886,22 +1741,17 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>241</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>1</v>
+        <v>362</v>
+      </c>
+      <c r="G32" t="n">
+        <v>218</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
@@ -1932,22 +1782,17 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>359</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
+        <v>425</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
@@ -1978,22 +1823,17 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="G34" t="n">
+        <v>528</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
@@ -2024,22 +1864,17 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="G35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
@@ -2070,24 +1905,62 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H36" t="b">
-        <v>0</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>69</v>
+      </c>
+      <c r="G37" t="n">
+        <v>75</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -2102,7 +1975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2141,15 +2014,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2161,43 +2029,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·《天空之城》久石让·宫崎骏动漫经典作品音乐会|浙江电影爱乐乐团</t>
+          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 19:30-01.27 21:00</t>
+          <t>2024.01.29 18:00-01.29 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>89</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80903</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/jZsCde491705396008863.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
         </is>
       </c>
     </row>
@@ -2207,43 +2070,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
+          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林广场29号 杭州剧院</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.29 18:00-01.29 21:00</t>
+          <t>2024.01.31 19:30-01.31 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
         </is>
       </c>
     </row>
@@ -2253,43 +2113,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>58</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2154,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2345,43 +2195,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -2391,87 +2236,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>180</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
@@ -2488,7 +2282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2527,15 +2321,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2566,22 +2355,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>190</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="G2" t="n">
+        <v>108</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80137</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80137</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/TRE8uUjw1703229665251.png</t>
         </is>
@@ -2598,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,15 +2421,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2676,22 +2455,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>190</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="G2" t="n">
+        <v>108</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80137</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80137</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/TRE8uUjw1703229665251.png</t>
         </is>
@@ -2722,22 +2496,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>990</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
+        <v>1015</v>
+      </c>
+      <c r="G3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79906</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79906</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/fsCnC2E81702888590146.jpeg</t>
         </is>
@@ -2749,43 +2518,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·VOCALOID ONLY（取消）</t>
+          <t>杭州·文豪野犬舞会ONLY:横滨晚宴（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九环路7号 杭州鑫牛大厦</t>
+          <t>九龙大道227号 七里香溪别墅园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 17:00</t>
+          <t>2024.01.28 10:00-01.28 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>845</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H4" t="b">
-        <v>1</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77627</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80374</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/2Znkbtbv1704250050863.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/n3gFbUkJ1698202692701.jpeg</t>
         </is>
       </c>
     </row>
@@ -2795,43 +2561,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·《天空之城》久石让·宫崎骏动漫经典作品音乐会|浙江电影爱乐乐团</t>
+          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.27 19:30-01.27 21:00</t>
+          <t>2024.01.29 18:00-01.29 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="G5" t="n">
+        <v>89</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80903</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/jZsCde491705396008863.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
         </is>
       </c>
     </row>
@@ -2841,43 +2602,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·文豪野犬舞会ONLY:横滨晚宴（取消）</t>
+          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>九龙大道227号 七里香溪别墅园</t>
+          <t>武林广场29号 杭州剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.01.31 19:30-01.31 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>845</v>
+        <v>28</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H6" t="b">
-        <v>1</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77627</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/n3gFbUkJ1698202692701.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
         </is>
       </c>
     </row>
@@ -2887,43 +2645,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
+          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.29 18:00-01.29 21:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2933,43 +2686,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>7474</v>
+      </c>
+      <c r="G8" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -2984,38 +2732,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7065</v>
+        <v>2715</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -3030,38 +2775,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2718</v>
+        <v>926</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -3071,43 +2813,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>915</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>284</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -3122,38 +2859,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>271</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>780</v>
+      </c>
+      <c r="G12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -3163,43 +2895,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>760</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>574</v>
+      </c>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -3209,43 +2936,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>538</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="G14" t="n">
+        <v>88</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -3255,43 +2977,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.07 10:00-02.07 17:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="G15" t="n">
+        <v>52</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -3301,43 +3018,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>374</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
+          <t>已售罄</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -3347,43 +3061,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·心动次元动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>852</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/XOt6GoR71706165982147.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3102,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3408,28 +3117,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>370</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G18" t="n">
+        <v>58</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3439,43 +3143,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>834</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>2993</v>
+      </c>
+      <c r="G19" t="n">
+        <v>65</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3490,38 +3189,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
+        <v>174</v>
+      </c>
+      <c r="G20" t="n">
+        <v>138</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3531,43 +3225,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2825</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="G21" t="n">
+        <v>59</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3577,43 +3266,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>139</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>90</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3623,43 +3307,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>697</v>
+      </c>
+      <c r="G23" t="n">
+        <v>65</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3674,38 +3353,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>745</v>
+      </c>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3715,43 +3389,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>192</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
         <v>1</v>
       </c>
+      <c r="G25" t="n">
+        <v>180</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,43 +3430,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>734</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>70</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -3807,43 +3471,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>438</v>
+      </c>
+      <c r="G27" t="n">
+        <v>89</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3853,43 +3512,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G28" t="n">
+        <v>50</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3899,43 +3553,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>419</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>184</v>
+      </c>
+      <c r="G29" t="n">
+        <v>70</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3599,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3964,24 +3613,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>119</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>1</v>
+        <v>202</v>
+      </c>
+      <c r="G30" t="n">
+        <v>65</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,43 +3635,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>178</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
+        <v>208</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -4042,7 +3681,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4052,28 +3691,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
+        <v>236</v>
+      </c>
+      <c r="G32" t="n">
+        <v>218</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -4088,38 +3722,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>148</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>1</v>
+        <v>121</v>
+      </c>
+      <c r="G33" t="n">
+        <v>88</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -4134,38 +3763,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>111</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="G34" t="n">
+        <v>68</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -4180,38 +3804,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>62</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>1</v>
+        <v>220</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -4226,38 +3845,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>167</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G36" t="n">
+        <v>78</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4272,38 +3886,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -4313,43 +3924,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
+        <v>363</v>
+      </c>
+      <c r="G38" t="n">
+        <v>218</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4359,43 +3965,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>241</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="H39" t="b">
-        <v>1</v>
+        <v>425</v>
+      </c>
+      <c r="G39" t="n">
+        <v>75</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4405,12 +4006,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4420,28 +4021,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>359</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G40" t="n">
+        <v>528</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4451,43 +4047,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="H41" t="b">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="G41" t="n">
+        <v>70</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4502,12 +4093,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4516,24 +4107,21 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4543,43 +4131,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>225</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="G43" t="n">
+        <v>75</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4608,22 +4191,17 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>180</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州.第32届 中二病 原神x星穹only</t>
+          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.27 11:00-01.28 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1015</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/fsCnC2E81702888590146.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,40 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·文豪野犬舞会ONLY:横滨晚宴（取消）</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>九龙大道227号 七里香溪别墅园</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>845</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>7593</v>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/n3gFbUkJ1698202692701.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -571,33 +569,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>55</v>
+        <v>2714</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -612,33 +612,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7474</v>
-      </c>
-      <c r="G5" t="n">
-        <v>70</v>
+        <v>929</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,40 +650,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2715</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>285</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -706,25 +706,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>926</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>793</v>
+      </c>
+      <c r="G7" t="n">
+        <v>68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>284</v>
+        <v>580</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +773,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>780</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -816,38 +814,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>574</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,38 +855,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
-      </c>
-      <c r="G11" t="n">
-        <v>88</v>
+        <v>376</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -898,38 +898,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>856</v>
       </c>
       <c r="G12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -939,40 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>374</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>3044</v>
+      </c>
+      <c r="G13" t="n">
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -982,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>852</v>
+        <v>185</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2993</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>174</v>
+        <v>712</v>
       </c>
       <c r="G16" t="n">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1105,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>749</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1144,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>697</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>745</v>
+        <v>443</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1226,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,38 +1267,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>438</v>
+        <v>196</v>
       </c>
       <c r="G21" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,33 +1313,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1351,38 +1349,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1392,38 +1390,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>202</v>
-      </c>
-      <c r="G24" t="n">
-        <v>65</v>
+        <v>281</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1438,33 +1438,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1479,33 +1479,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="G26" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>121</v>
+        <v>234</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1561,33 +1561,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1616,19 +1616,21 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>220</v>
-      </c>
-      <c r="G29" t="n">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1640,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
-      </c>
-      <c r="G30" t="n">
-        <v>78</v>
+        <v>484</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1679,40 +1683,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>440</v>
+      </c>
+      <c r="G31" t="n">
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1722,38 +1724,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>362</v>
+        <v>26</v>
       </c>
       <c r="G32" t="n">
-        <v>218</v>
+        <v>528</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1763,38 +1765,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>425</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,38 +1806,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>23</v>
-      </c>
-      <c r="G34" t="n">
-        <v>528</v>
+        <v>225</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1845,120 +1849,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>226</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>69</v>
-      </c>
-      <c r="G37" t="n">
-        <v>75</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
@@ -2048,7 +1968,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
         <v>89</v>
@@ -2355,7 +2275,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2382,7 +2302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2455,7 +2375,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2477,38 +2397,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州.第32届 中二病 原神x星穹only</t>
+          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 11:00-01.28 17:00</t>
+          <t>2024.01.29 18:00-01.29 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1015</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/fsCnC2E81702888590146.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
         </is>
       </c>
     </row>
@@ -2518,26 +2438,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·文豪野犬舞会ONLY:横滨晚宴（取消）</t>
+          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>九龙大道227号 七里香溪别墅园</t>
+          <t>武林广场29号 杭州剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.28 10:00-01.28 17:00</t>
+          <t>2024.01.31 19:30-01.31 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>845</v>
+        <v>28</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2546,12 +2466,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77627</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/n3gFbUkJ1698202692701.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
         </is>
       </c>
     </row>
@@ -2561,38 +2481,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
+          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.29 18:00-01.29 21:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2602,40 +2522,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>7593</v>
+      </c>
+      <c r="G6" t="n">
+        <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -2650,33 +2568,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>55</v>
+        <v>2714</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -2691,33 +2611,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7474</v>
-      </c>
-      <c r="G8" t="n">
-        <v>70</v>
+        <v>929</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -2727,40 +2649,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2715</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>285</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2690,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2785,25 +2705,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>926</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>793</v>
+      </c>
+      <c r="G10" t="n">
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -2813,38 +2731,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>284</v>
+        <v>580</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -2854,38 +2772,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>780</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -2895,38 +2813,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>574</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -2936,38 +2854,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
-      </c>
-      <c r="G14" t="n">
-        <v>88</v>
+        <v>376</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -2977,38 +2897,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>856</v>
       </c>
       <c r="G15" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3018,12 +2938,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3033,25 +2953,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>374</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="G16" t="n">
+        <v>58</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3061,38 +2979,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>852</v>
+        <v>3044</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3107,33 +3025,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3143,38 +3061,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2993</v>
+        <v>79</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3184,38 +3102,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3225,38 +3143,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>70</v>
+        <v>712</v>
       </c>
       <c r="G21" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3271,33 +3189,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>749</v>
       </c>
       <c r="G22" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3307,38 +3225,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>697</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3348,38 +3266,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>745</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
         </is>
       </c>
     </row>
@@ -3389,38 +3307,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="G25" t="n">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3430,38 +3348,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3471,38 +3389,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>438</v>
+        <v>196</v>
       </c>
       <c r="G27" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3517,33 +3435,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3553,38 +3471,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3594,38 +3512,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>202</v>
-      </c>
-      <c r="G30" t="n">
-        <v>65</v>
+        <v>281</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3640,33 +3560,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3681,33 +3601,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="G32" t="n">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3642,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3736,19 +3656,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>121</v>
+        <v>234</v>
       </c>
       <c r="G33" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3763,33 +3683,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3724,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3818,19 +3738,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>220</v>
-      </c>
-      <c r="G35" t="n">
-        <v>60</v>
+        <v>18</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -3840,38 +3762,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
-      </c>
-      <c r="G36" t="n">
-        <v>78</v>
+        <v>484</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3881,40 +3805,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>440</v>
+      </c>
+      <c r="G37" t="n">
+        <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -3924,38 +3846,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>363</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>218</v>
+        <v>528</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3965,38 +3887,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>425</v>
+        <v>18</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4006,38 +3928,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
-      </c>
-      <c r="G40" t="n">
-        <v>528</v>
+        <v>225</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4047,38 +3971,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4088,120 +4012,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>226</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>180</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>69</v>
-      </c>
-      <c r="G43" t="n">
-        <v>75</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>7</v>
-      </c>
-      <c r="G44" t="n">
-        <v>180</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7593</v>
+        <v>7640</v>
       </c>
       <c r="G3" t="n">
         <v>70</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3044</v>
+        <v>3068</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G25" t="n">
         <v>88</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G32" t="n">
         <v>528</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>180</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7593</v>
+        <v>7640</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G12" t="n">
         <v>88</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3044</v>
+        <v>3068</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G18" t="n">
         <v>138</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="G25" t="n">
         <v>89</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G27" t="n">
         <v>70</v>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G32" t="n">
         <v>68</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G42" t="n">
         <v>180</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7640</v>
+        <v>7799</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3068</v>
+        <v>3122</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G25" t="n">
         <v>88</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1561,33 +1561,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1602,35 +1602,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>78</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1640,40 +1638,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>492</v>
+        <v>17</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1683,38 +1681,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>454</v>
-      </c>
-      <c r="G31" t="n">
-        <v>75</v>
+        <v>500</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>28</v>
+        <v>494</v>
       </c>
       <c r="G32" t="n">
-        <v>528</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1765,38 +1765,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>528</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1806,40 +1806,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>225</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>528</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1849,36 +1847,120 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" t="n">
+        <v>70</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>225</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>2024-04-05</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>83</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F37" t="n">
+        <v>92</v>
+      </c>
+      <c r="G37" t="n">
         <v>75</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
@@ -1968,10 +2050,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G2" t="n">
-        <v>108</v>
+        <v>36</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2052,7 +2136,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>58</v>
@@ -2302,7 +2386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,10 +2500,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G3" t="n">
-        <v>108</v>
+        <v>36</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2500,7 +2586,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -2541,10 +2627,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7640</v>
+        <v>7800</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2582,7 +2668,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2625,7 +2711,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2668,7 +2754,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -2709,7 +2795,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -2750,7 +2836,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -2791,7 +2877,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
         <v>88</v>
@@ -2832,7 +2918,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
         <v>52</v>
@@ -2873,7 +2959,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2916,7 +3002,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2957,7 +3043,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
         <v>58</v>
@@ -2998,7 +3084,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3068</v>
+        <v>3122</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -3039,7 +3125,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G18" t="n">
         <v>138</v>
@@ -3080,7 +3166,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
         <v>59</v>
@@ -3162,7 +3248,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -3203,7 +3289,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -3285,7 +3371,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -3297,7 +3383,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/W36q04zR1705649316435.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3412,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G25" t="n">
         <v>89</v>
@@ -3408,7 +3494,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="G27" t="n">
         <v>70</v>
@@ -3449,7 +3535,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -3490,7 +3576,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3531,7 +3617,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3574,7 +3660,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -3615,7 +3701,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
         <v>68</v>
@@ -3656,7 +3742,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3683,33 +3769,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3724,35 +3810,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="G35" t="n">
+        <v>78</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3762,40 +3846,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>492</v>
+        <v>17</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -3805,38 +3889,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>454</v>
-      </c>
-      <c r="G37" t="n">
-        <v>75</v>
+        <v>500</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3932,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3861,23 +3947,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28</v>
+        <v>494</v>
       </c>
       <c r="G38" t="n">
-        <v>528</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -3887,38 +3973,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>528</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -3928,40 +4014,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>225</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>528</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3971,38 +4055,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4012,36 +4096,120 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>225</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>92</v>
+      </c>
+      <c r="G43" t="n">
+        <v>75</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F44" t="n">
         <v>8</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G44" t="n">
         <v>180</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7799</v>
+        <v>7880</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3122</v>
+        <v>3148</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G25" t="n">
         <v>88</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
         <v>79</v>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -1977,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2031,26 +2031,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
+          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林广场29号 杭州剧院</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.29 18:00-01.29 21:00</t>
+          <t>2024.01.31 19:30-01.31 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
         </is>
       </c>
     </row>
@@ -2074,40 +2074,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2117,38 +2115,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2158,38 +2156,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -2199,77 +2197,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>180</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>180</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
@@ -2359,7 +2316,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2386,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2459,7 +2416,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2481,26 +2438,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·向着遥远的未来出发 miriちゃん生日SP</t>
+          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林广场29号 杭州剧院</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.29 18:00-01.29 21:00</t>
+          <t>2024.01.31 19:30-01.31 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2509,12 +2466,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79894</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FmxbBxzF1702885022073.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
         </is>
       </c>
     </row>
@@ -2524,40 +2481,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2572,33 +2527,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>7880</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -2613,33 +2568,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7800</v>
-      </c>
-      <c r="G6" t="n">
-        <v>80</v>
+        <v>2711</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -2654,35 +2611,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2711</v>
+        <v>935</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -2692,40 +2649,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>934</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>290</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -2740,33 +2695,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>289</v>
+        <v>801</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -2776,38 +2731,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>797</v>
+        <v>606</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -2817,38 +2772,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>595</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -2863,33 +2818,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -2899,38 +2854,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
-      </c>
-      <c r="G13" t="n">
-        <v>52</v>
+        <v>379</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -2945,35 +2902,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>379</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>864</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -2983,38 +2938,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>861</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3029,33 +2984,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>3148</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3025,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3084,19 +3039,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3122</v>
+        <v>201</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3106,38 +3061,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="G18" t="n">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3147,38 +3102,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
         <v>90</v>
       </c>
-      <c r="G19" t="n">
-        <v>59</v>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3193,33 +3148,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>738</v>
       </c>
       <c r="G20" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3234,33 +3189,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3270,38 +3225,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>754</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3311,38 +3266,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3357,33 +3312,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>46</v>
+        <v>457</v>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3393,38 +3348,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>453</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3439,33 +3394,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3435,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3494,19 +3449,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3516,38 +3471,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>218</v>
+        <v>314</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3517,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3572,23 +3527,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>300</v>
-      </c>
-      <c r="G29" t="n">
-        <v>60</v>
+        <v>287</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3603,35 +3560,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>285</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>131</v>
+      </c>
+      <c r="G30" t="n">
+        <v>88</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3646,33 +3601,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="G31" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3687,33 +3642,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3728,33 +3683,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3769,33 +3724,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3810,33 +3765,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
-      </c>
-      <c r="G35" t="n">
-        <v>78</v>
+        <v>17</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -3846,40 +3803,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>501</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3889,40 +3846,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>500</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>520</v>
+      </c>
+      <c r="G37" t="n">
+        <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3892,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3947,23 +3902,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>494</v>
+        <v>22</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3928,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3988,23 +3943,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G39" t="n">
         <v>528</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4014,38 +3969,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G40" t="n">
-        <v>528</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4060,12 +4015,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4074,19 +4029,21 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
-      </c>
-      <c r="G41" t="n">
-        <v>70</v>
+        <v>224</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4096,40 +4053,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>225</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="G42" t="n">
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4139,77 +4094,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" t="n">
-        <v>180</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7880</v>
+        <v>8004</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3148</v>
+        <v>3279</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G25" t="n">
         <v>88</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
         <v>79</v>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1847,38 +1847,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1907,21 +1907,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>224</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="G36" t="n">
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1931,36 +1929,79 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>226</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>2024-04-05</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>97</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F38" t="n">
+        <v>104</v>
+      </c>
+      <c r="G38" t="n">
         <v>75</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
@@ -2219,7 +2260,7 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>180</v>
+        <v>408</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2316,7 +2357,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2343,7 +2384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,7 +2457,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2500,7 +2541,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -2541,7 +2582,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7880</v>
+        <v>8004</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -2625,7 +2666,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2668,7 +2709,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -2709,7 +2750,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -2750,7 +2791,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="G10" t="n">
         <v>40</v>
@@ -2791,7 +2832,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
         <v>88</v>
@@ -2832,7 +2873,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
         <v>52</v>
@@ -2916,7 +2957,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2998,7 +3039,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3148</v>
+        <v>3279</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -3039,7 +3080,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G17" t="n">
         <v>138</v>
@@ -3080,7 +3121,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -3162,7 +3203,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3203,7 +3244,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -3285,7 +3326,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3326,7 +3367,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="G24" t="n">
         <v>89</v>
@@ -3408,7 +3449,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -3449,7 +3490,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -3490,7 +3531,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3531,7 +3572,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3574,7 +3615,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G30" t="n">
         <v>88</v>
@@ -3615,7 +3656,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3656,7 +3697,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3697,7 +3738,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G33" t="n">
         <v>79</v>
@@ -3822,7 +3863,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3865,7 +3906,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -3906,7 +3947,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
@@ -3947,7 +3988,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G39" t="n">
         <v>528</v>
@@ -3969,38 +4010,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4056,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4029,21 +4070,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>224</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="G41" t="n">
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4053,38 +4092,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>97</v>
-      </c>
-      <c r="G42" t="n">
-        <v>75</v>
+        <v>226</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4094,36 +4135,77 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>104</v>
+      </c>
+      <c r="G43" t="n">
+        <v>75</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F44" t="n">
         <v>8</v>
       </c>
-      <c r="G43" t="n">
-        <v>180</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="G44" t="n">
+        <v>408</v>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8004</v>
+        <v>8100</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3279</v>
+        <v>3322</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>232</v>
+        <v>736</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G25" t="n">
         <v>88</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
         <v>79</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G35" t="n">
         <v>89</v>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8004</v>
+        <v>8100</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="G10" t="n">
         <v>40</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G11" t="n">
         <v>88</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
         <v>52</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3279</v>
+        <v>3322</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G17" t="n">
         <v>138</v>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G24" t="n">
         <v>89</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>232</v>
+        <v>736</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G30" t="n">
         <v>88</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G33" t="n">
         <v>79</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G39" t="n">
         <v>528</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G40" t="n">
         <v>89</v>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G41" t="n">
         <v>70</v>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G43" t="n">
         <v>75</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8100</v>
+        <v>8249</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3322</v>
+        <v>3551</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1226,38 +1226,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1272,33 +1272,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>283</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>736</v>
+        <v>453</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -1349,38 +1349,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>355</v>
+        <v>1338</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,25 +1405,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>288</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>381</v>
+      </c>
+      <c r="G24" t="n">
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1438,33 +1436,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
-      </c>
-      <c r="G25" t="n">
-        <v>88</v>
+        <v>288</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1479,33 +1479,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G26" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1520,33 +1520,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>296</v>
+        <v>133</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1561,33 +1561,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>34</v>
+        <v>309</v>
       </c>
       <c r="G28" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1602,33 +1602,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1643,35 +1643,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1011</v>
+      </c>
+      <c r="G30" t="n">
+        <v>78</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1681,40 +1679,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>506</v>
+        <v>17</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1724,38 +1722,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>585</v>
-      </c>
-      <c r="G32" t="n">
-        <v>75</v>
+        <v>509</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1780,23 +1780,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>609</v>
       </c>
       <c r="G33" t="n">
-        <v>528</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1821,23 +1821,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1847,38 +1847,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G35" t="n">
-        <v>89</v>
+        <v>528</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1888,38 +1888,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1948,21 +1948,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>226</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>70</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1972,36 +1970,79 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>227</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>2024-04-05</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>109</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F39" t="n">
+        <v>116</v>
+      </c>
+      <c r="G39" t="n">
         <v>75</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
@@ -2018,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,7 +2175,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
         <v>58</v>
@@ -2175,7 +2216,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>90</v>
@@ -2216,7 +2257,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>180</v>
@@ -2238,38 +2279,161 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>曙光路31号 浙江音乐厅</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024.03.08 19:30-03.08 21:00</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024.03.16 19:00-03.16 21:00</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>72</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G8" t="n">
         <v>408</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>武林路77号 文化馆小剧场</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024.05.01 19:30-05.01 21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2521,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2384,7 +2548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,7 +2621,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2541,7 +2705,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>55</v>
@@ -2582,7 +2746,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8100</v>
+        <v>8249</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -2623,7 +2787,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2666,7 +2830,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2709,7 +2873,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -2750,7 +2914,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -2791,7 +2955,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="G10" t="n">
         <v>40</v>
@@ -2832,7 +2996,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G11" t="n">
         <v>88</v>
@@ -2873,7 +3037,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
         <v>52</v>
@@ -2914,7 +3078,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2957,7 +3121,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2998,7 +3162,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
         <v>58</v>
@@ -3039,7 +3203,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3322</v>
+        <v>3551</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -3080,7 +3244,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G17" t="n">
         <v>138</v>
@@ -3121,7 +3285,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
         <v>59</v>
@@ -3162,7 +3326,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>90</v>
@@ -3203,7 +3367,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3244,7 +3408,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -3285,7 +3449,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>180</v>
@@ -3367,7 +3531,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="G24" t="n">
         <v>89</v>
@@ -3389,38 +3553,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3430,38 +3594,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>283</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3476,33 +3640,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>736</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3512,38 +3676,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>355</v>
+        <v>454</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3553,40 +3717,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>288</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1338</v>
+      </c>
+      <c r="G29" t="n">
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3601,33 +3763,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>135</v>
+        <v>381</v>
       </c>
       <c r="G30" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3642,33 +3804,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>130</v>
-      </c>
-      <c r="G31" t="n">
-        <v>68</v>
+        <v>288</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3847,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3697,19 +3861,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>296</v>
+        <v>139</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3724,33 +3888,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="G33" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3765,33 +3929,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3970,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3820,21 +3984,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>17</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>309</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3844,40 +4006,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>506</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="G36" t="n">
+        <v>79</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3887,38 +4047,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>585</v>
+        <v>1011</v>
       </c>
       <c r="G37" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3928,38 +4088,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28</v>
-      </c>
-      <c r="G38" t="n">
-        <v>528</v>
+        <v>17</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -3969,38 +4131,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>38</v>
-      </c>
-      <c r="G39" t="n">
-        <v>528</v>
+        <v>509</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4010,38 +4174,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>609</v>
       </c>
       <c r="G40" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4051,38 +4215,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>528</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4092,40 +4256,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>226</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="G42" t="n">
+        <v>528</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4135,38 +4297,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4176,38 +4338,204 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>25</v>
+      </c>
+      <c r="G44" t="n">
+        <v>70</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>227</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>116</v>
+      </c>
+      <c r="G46" t="n">
+        <v>75</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>2024-04-27</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F47" t="n">
         <v>8</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G47" t="n">
         <v>408</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>武林路77号 文化馆小剧场</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.05.01 19:30-05.01 21:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>120</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
       </c>
     </row>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8249</v>
+        <v>8315</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3551</v>
+        <v>3575</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>453</v>
+        <v>799</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G29" t="n">
         <v>79</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G37" t="n">
         <v>70</v>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2059,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2113,40 +2113,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="G2" t="n">
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2156,38 +2154,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2197,38 +2195,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -2238,38 +2236,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2279,38 +2277,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -2320,38 +2318,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>72</v>
+        <v>408</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
       </c>
     </row>
@@ -2361,77 +2359,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>408</v>
+        <v>120</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>武林路77号 文化馆小剧场</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2024.05.01 19:30-05.01 21:00</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
@@ -2521,7 +2478,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2548,7 +2505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,7 +2578,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2643,40 +2600,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·《爱永恒》理查德·克莱德曼2024新年钢琴音乐会</t>
+          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>武林广场29号 杭州剧院</t>
+          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.31 19:30-01.31 21:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202309/LLUVyWRA1694484996221.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
         </is>
       </c>
     </row>
@@ -2691,33 +2646,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>8315</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -2732,33 +2687,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8249</v>
-      </c>
-      <c r="G5" t="n">
-        <v>80</v>
+        <v>2707</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -2773,35 +2730,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2708</v>
+        <v>949</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -2811,40 +2768,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>947</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>305</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -2859,33 +2814,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>305</v>
+        <v>820</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -2895,38 +2850,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>814</v>
+        <v>640</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -2936,38 +2891,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>633</v>
+        <v>116</v>
       </c>
       <c r="G10" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -2982,33 +2937,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -3018,38 +2973,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
-      </c>
-      <c r="G12" t="n">
-        <v>52</v>
+        <v>381</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -3064,35 +3021,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>380</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>879</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3102,38 +3057,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>877</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3148,33 +3103,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>3575</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3144,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3203,19 +3158,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3551</v>
+        <v>248</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3225,38 +3180,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>239</v>
+        <v>133</v>
       </c>
       <c r="G17" t="n">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3266,38 +3221,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3312,33 +3267,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>777</v>
       </c>
       <c r="G19" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3353,33 +3308,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3389,38 +3344,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>764</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3430,38 +3385,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3476,33 +3431,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>483</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3512,38 +3467,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3553,38 +3508,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3594,38 +3549,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3640,33 +3595,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>800</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3636,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3695,19 +3650,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>454</v>
+        <v>1343</v>
       </c>
       <c r="G28" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3717,38 +3672,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1338</v>
+        <v>394</v>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3718,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3773,23 +3728,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>381</v>
-      </c>
-      <c r="G30" t="n">
-        <v>60</v>
+        <v>288</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3804,35 +3761,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>288</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="G31" t="n">
+        <v>88</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3847,33 +3802,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>139</v>
       </c>
       <c r="G32" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3888,33 +3843,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3929,33 +3884,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G34" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3970,33 +3925,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>309</v>
+        <v>46</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -4011,33 +3966,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>41</v>
+        <v>1011</v>
       </c>
       <c r="G36" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4052,33 +4007,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G37" t="n">
-        <v>78</v>
+        <v>17</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -4088,40 +4045,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>17</v>
+        <v>508</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4131,40 +4088,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>509</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>621</v>
+      </c>
+      <c r="G39" t="n">
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4134,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4189,23 +4144,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>609</v>
+        <v>37</v>
       </c>
       <c r="G40" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4170,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4230,23 +4185,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G41" t="n">
         <v>528</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4256,38 +4211,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G42" t="n">
-        <v>528</v>
+        <v>89</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4297,38 +4252,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G43" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4298,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4357,19 +4312,21 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>25</v>
-      </c>
-      <c r="G44" t="n">
-        <v>70</v>
+        <v>227</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4379,40 +4336,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>227</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>124</v>
+      </c>
+      <c r="G45" t="n">
+        <v>75</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4422,38 +4377,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>75</v>
+        <v>408</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
       </c>
     </row>
@@ -4463,77 +4418,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>408</v>
+        <v>120</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>武林路77号 文化馆小剧场</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.05.01 19:30-05.01 21:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>120</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8315</v>
+        <v>8431</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3575</v>
+        <v>3641</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>799</v>
+        <v>1117</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1450,12 +1450,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>288</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>289</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1493,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -1534,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1575,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1616,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
         <v>79</v>
@@ -1657,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -1741,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1784,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1825,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1866,7 +1864,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -1907,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1948,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G37" t="n">
         <v>70</v>
@@ -2032,7 +2030,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2045,6 +2043,47 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>杭州·白日梦次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>黄姑山路51-4号 0101park</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.20 10:00-04.21 18:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>68</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2171,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2478,7 +2517,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2505,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2578,7 +2617,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2619,7 +2658,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -2660,7 +2699,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8315</v>
+        <v>8431</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -2701,7 +2740,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2744,7 +2783,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2787,7 +2826,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -2828,7 +2867,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2869,7 +2908,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
@@ -2910,7 +2949,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G10" t="n">
         <v>88</v>
@@ -2951,7 +2990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
         <v>52</v>
@@ -2992,7 +3031,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3035,7 +3074,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -3076,7 +3115,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
         <v>58</v>
@@ -3117,7 +3156,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3575</v>
+        <v>3641</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -3158,7 +3197,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G16" t="n">
         <v>138</v>
@@ -3180,38 +3219,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3226,33 +3265,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>786</v>
       </c>
       <c r="G18" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3267,33 +3306,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3303,38 +3342,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>764</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3344,38 +3383,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3390,33 +3429,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>491</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3426,38 +3465,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>483</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3467,38 +3506,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3508,38 +3547,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3554,33 +3593,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>1117</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3634,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3609,19 +3648,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>800</v>
+        <v>1350</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3631,38 +3670,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1343</v>
+        <v>420</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3716,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3687,23 +3726,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>394</v>
+        <v>289</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3771,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>288</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>289</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3775,7 +3812,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -3816,7 +3853,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G32" t="n">
         <v>68</v>
@@ -3898,7 +3935,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3939,7 +3976,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
         <v>79</v>
@@ -3980,7 +4017,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="G36" t="n">
         <v>78</v>
@@ -4064,7 +4101,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4107,7 +4144,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -4148,7 +4185,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G40" t="n">
         <v>528</v>
@@ -4189,7 +4226,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G41" t="n">
         <v>528</v>
@@ -4230,7 +4267,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G42" t="n">
         <v>89</v>
@@ -4271,7 +4308,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G43" t="n">
         <v>70</v>
@@ -4355,7 +4392,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4377,38 +4414,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
       </c>
     </row>
@@ -4418,36 +4455,77 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>金沙大道681号 金沙湖大剧院</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.04.27 19:30-04.27 21:30</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>408</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>1</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G48" t="n">
         <v>120</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8431</v>
+        <v>8507</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3641</v>
+        <v>3680</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G15" t="n">
         <v>59</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1117</v>
+        <v>1320</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1450,10 +1450,12 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>289</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
+        <v>292</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1491,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -1532,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1573,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1614,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G29" t="n">
         <v>79</v>
@@ -1739,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1782,7 +1784,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1823,7 +1825,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1864,7 +1866,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -1905,7 +1907,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1946,7 +1948,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G37" t="n">
         <v>70</v>
@@ -2030,7 +2032,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2071,7 +2073,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -2658,7 +2660,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -2699,7 +2701,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8431</v>
+        <v>8507</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -2826,7 +2828,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G7" t="n">
         <v>50</v>
@@ -2867,7 +2869,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2908,7 +2910,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="G9" t="n">
         <v>40</v>
@@ -2949,7 +2951,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G10" t="n">
         <v>88</v>
@@ -2990,7 +2992,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
         <v>52</v>
@@ -3074,7 +3076,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -3156,7 +3158,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3641</v>
+        <v>3680</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -3197,7 +3199,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G16" t="n">
         <v>138</v>
@@ -3219,38 +3221,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3265,33 +3267,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>786</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3306,33 +3308,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>771</v>
+        <v>790</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3342,38 +3344,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>773</v>
       </c>
       <c r="G20" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3383,38 +3385,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3429,33 +3431,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>491</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3465,38 +3467,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>494</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3506,38 +3508,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3547,38 +3549,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3593,33 +3595,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1117</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3636,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3648,19 +3650,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1350</v>
+        <v>1320</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3670,38 +3672,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>420</v>
+        <v>1354</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3718,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3726,23 +3728,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>289</v>
+        <v>435</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3771,10 +3773,12 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>289</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
+        <v>292</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3812,7 +3816,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -3853,7 +3857,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G32" t="n">
         <v>68</v>
@@ -3935,7 +3939,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3976,7 +3980,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G35" t="n">
         <v>79</v>
@@ -4101,7 +4105,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4144,7 +4148,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -4185,7 +4189,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
         <v>528</v>
@@ -4226,7 +4230,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G41" t="n">
         <v>528</v>
@@ -4267,7 +4271,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G42" t="n">
         <v>89</v>
@@ -4308,7 +4312,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
         <v>70</v>
@@ -4392,7 +4396,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4433,7 +4437,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8507</v>
+        <v>8703</v>
       </c>
       <c r="G3" t="n">
         <v>80</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3680</v>
+        <v>3745</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>19.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1320</v>
+        <v>1360</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G29" t="n">
         <v>79</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1929,38 +1929,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1989,21 +1989,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>227</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="G38" t="n">
+        <v>70</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -2013,38 +2011,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -2054,36 +2052,202 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.04 10:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>227</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>183</v>
+      </c>
+      <c r="G41" t="n">
+        <v>75</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>246</v>
+      </c>
+      <c r="G42" t="n">
+        <v>248</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>17</v>
+      </c>
+      <c r="G43" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="F44" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" t="n">
         <v>68</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2100,7 +2264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2236,38 +2400,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -2277,38 +2441,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -2318,38 +2482,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>72</v>
+        <v>388</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -2359,38 +2523,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>408</v>
+        <v>90</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2400,36 +2564,118 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2024.03.16 19:00-03.16 21:00</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>72</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>金沙大道681号 金沙湖大剧院</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024.04.27 19:30-04.27 21:30</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>408</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>120</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
@@ -2519,7 +2765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2546,7 +2792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,7 +2865,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2660,7 +2906,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -2701,7 +2947,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8507</v>
+        <v>8704</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -2728,35 +2974,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·浙江蔚蓝档案only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2706</v>
+        <v>956</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
         </is>
       </c>
     </row>
@@ -2766,40 +3012,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>952</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>313</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -2814,33 +3058,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>石祥路242号 首开公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>310</v>
+        <v>826</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -2850,38 +3094,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>823</v>
+        <v>676</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -2891,38 +3135,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>657</v>
+        <v>125</v>
       </c>
       <c r="G9" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -2937,33 +3181,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="G10" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -2973,38 +3217,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
-      </c>
-      <c r="G11" t="n">
-        <v>52</v>
+        <v>383</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -3019,35 +3265,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>382</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>899</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3057,38 +3301,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>895</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3103,33 +3347,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>3745</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3388,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3158,19 +3402,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3680</v>
+        <v>277</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3180,38 +3424,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="G16" t="n">
-        <v>138</v>
+        <v>19.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3221,38 +3465,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>145</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3267,33 +3511,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3566,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -3363,7 +3607,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
@@ -3426,38 +3670,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>388</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3472,33 +3716,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>494</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3508,38 +3752,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>497</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3549,38 +3793,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3590,38 +3834,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3636,33 +3880,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1320</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3921,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3691,19 +3935,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3713,38 +3957,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>435</v>
+        <v>1359</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3759,7 +4003,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3769,25 +4013,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>292</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>461</v>
+      </c>
+      <c r="G30" t="n">
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3802,33 +4044,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>146</v>
-      </c>
-      <c r="G31" t="n">
-        <v>88</v>
+        <v>291</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3843,33 +4087,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3884,33 +4128,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="G33" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3925,33 +4169,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3966,33 +4210,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>58</v>
+        <v>359</v>
       </c>
       <c r="G35" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -4007,33 +4251,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1016</v>
+        <v>65</v>
       </c>
       <c r="G36" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -4048,35 +4292,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1019</v>
+      </c>
+      <c r="G37" t="n">
+        <v>78</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4347,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4148,7 +4390,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -4189,7 +4431,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G40" t="n">
         <v>528</v>
@@ -4230,7 +4472,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G41" t="n">
         <v>528</v>
@@ -4271,7 +4513,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G42" t="n">
         <v>89</v>
@@ -4293,38 +4535,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4339,12 +4581,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4353,21 +4595,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>227</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="G44" t="n">
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4377,38 +4617,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4418,38 +4658,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>黄姑山路51-4号 0101park</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>183</v>
       </c>
       <c r="G46" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4459,38 +4699,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
       </c>
     </row>
@@ -4500,36 +4740,77 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>金沙大道681号 金沙湖大剧院</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.04.27 19:30-04.27 21:30</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" t="n">
+        <v>408</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>1</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G49" t="n">
         <v>120</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8703</v>
-      </c>
-      <c r="G3" t="n">
-        <v>80</v>
+        <v>8972</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,11 +628,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -669,7 +671,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -710,7 +712,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -751,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>676</v>
+        <v>700</v>
       </c>
       <c r="G8" t="n">
         <v>40</v>
@@ -792,7 +794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G9" t="n">
         <v>88</v>
@@ -833,7 +835,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
         <v>52</v>
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -917,7 +919,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -958,7 +960,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3745</v>
+        <v>3834</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -999,7 +1001,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="G14" t="n">
         <v>138</v>
@@ -1040,7 +1042,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G15" t="n">
         <v>19.9</v>
@@ -1081,7 +1083,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1122,7 +1124,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1163,7 +1165,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -1204,7 +1206,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -1327,7 +1329,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1360</v>
+        <v>1389</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -1368,7 +1370,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -1409,7 +1411,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1450,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1493,7 +1495,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -1534,7 +1536,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -1575,7 +1577,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1616,7 +1618,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G29" t="n">
         <v>79</v>
@@ -1657,7 +1659,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -1741,7 +1743,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1784,7 +1786,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1825,7 +1827,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -1866,7 +1868,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -1907,7 +1909,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1948,7 +1950,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>99</v>
@@ -1989,7 +1991,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -2030,7 +2032,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>55</v>
@@ -2114,7 +2116,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -2155,7 +2157,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>246</v>
+        <v>342</v>
       </c>
       <c r="G42" t="n">
         <v>248</v>
@@ -2196,7 +2198,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G43" t="n">
         <v>39.9</v>
@@ -2237,7 +2239,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2337,7 +2339,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2419,7 +2421,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2765,7 +2767,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2865,7 +2867,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2906,10 +2908,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2928,38 +2930,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8704</v>
+        <v>318</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2971,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2984,25 +2986,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>956</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>832</v>
+      </c>
+      <c r="G5" t="n">
+        <v>68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -3012,38 +3012,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>313</v>
+        <v>700</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -3053,38 +3053,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>826</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -3094,38 +3094,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>676</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -3135,38 +3135,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>125</v>
-      </c>
-      <c r="G9" t="n">
-        <v>88</v>
+        <v>386</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -3176,38 +3178,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>77</v>
+        <v>901</v>
       </c>
       <c r="G10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3217,12 +3219,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3232,25 +3234,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>383</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3260,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>899</v>
+        <v>3835</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3306,33 +3306,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>290</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3342,38 +3342,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3745</v>
+        <v>172</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>19.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3383,38 +3383,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>277</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3424,38 +3424,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>159</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>19.9</v>
+        <v>388</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3470,33 +3470,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>803</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3511,33 +3511,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="G18" t="n">
-        <v>388</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3547,38 +3547,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>797</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3588,38 +3588,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>388</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3629,38 +3629,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3670,38 +3670,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="G22" t="n">
-        <v>388</v>
+        <v>89</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3711,38 +3711,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3752,38 +3752,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>497</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3793,38 +3793,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3834,38 +3834,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1389</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3880,33 +3880,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>1361</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3916,38 +3916,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1360</v>
+        <v>481</v>
       </c>
       <c r="G28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3957,38 +3957,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1359</v>
-      </c>
-      <c r="G29" t="n">
-        <v>65</v>
+        <v>293</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -4003,33 +4005,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>461</v>
+        <v>151</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -4044,35 +4046,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>291</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>174</v>
+      </c>
+      <c r="G31" t="n">
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -4087,33 +4087,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -4128,33 +4128,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>165</v>
+        <v>369</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -4169,33 +4169,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G34" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -4210,33 +4210,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>359</v>
+        <v>1022</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4246,38 +4246,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>65</v>
-      </c>
-      <c r="G36" t="n">
-        <v>79</v>
+        <v>512</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4287,38 +4289,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1019</v>
+        <v>718</v>
       </c>
       <c r="G37" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4328,40 +4330,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>510</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>56</v>
+      </c>
+      <c r="G38" t="n">
+        <v>528</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4386,23 +4386,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>691</v>
+        <v>59</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4412,38 +4412,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="G40" t="n">
-        <v>528</v>
+        <v>89</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4453,38 +4453,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>528</v>
+        <v>99</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4494,38 +4494,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G42" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4535,38 +4535,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4576,38 +4576,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="G44" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4617,38 +4617,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>342</v>
       </c>
       <c r="G45" t="n">
-        <v>55</v>
+        <v>248</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4677,19 +4677,19 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="G46" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,33 +487,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
+        <v>9014</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -528,21 +530,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8972</v>
+        <v>2700</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -551,12 +553,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,40 +568,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>富阳·原X铁X崩ONLY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>金桥北路1号 富阳东方茂</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.04 10:30-02.04 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2702</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>325</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·浙江蔚蓝档案only</t>
+          <t>杭州·偶像梦幻祭ONLY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -624,25 +624,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 18:00</t>
+          <t>2024.02.04 10:00-02.04 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>959</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>838</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77937</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/6wBH689v1702638477003.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
         </is>
       </c>
     </row>
@@ -652,38 +650,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>318</v>
+        <v>732</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,38 +691,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G7" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +732,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>700</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,38 +773,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
-      </c>
-      <c r="G9" t="n">
-        <v>88</v>
+        <v>388</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -816,38 +816,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>915</v>
       </c>
       <c r="G10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -857,40 +857,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>386</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>3975</v>
+      </c>
+      <c r="G11" t="n">
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -900,38 +898,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>901</v>
+        <v>311</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -941,38 +939,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3834</v>
+        <v>190</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>19.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -982,38 +980,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>290</v>
+        <v>810</v>
       </c>
       <c r="G14" t="n">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1021,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>172</v>
+        <v>780</v>
       </c>
       <c r="G15" t="n">
-        <v>19.9</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1062,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>803</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -1105,38 +1103,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>777</v>
+        <v>505</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1144,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1185,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1226,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>1431</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -1274,33 +1272,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>1369</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1310,38 +1308,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1389</v>
+        <v>508</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1351,38 +1349,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1361</v>
-      </c>
-      <c r="G23" t="n">
-        <v>65</v>
+        <v>293</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1397,33 +1397,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>481</v>
+        <v>158</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1438,35 +1438,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>293</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>180</v>
+      </c>
+      <c r="G25" t="n">
+        <v>68</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1479,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1495,19 +1493,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>151</v>
+        <v>380</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1522,33 +1520,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>174</v>
+        <v>76</v>
       </c>
       <c r="G27" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1563,33 +1561,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>369</v>
+        <v>1023</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1604,33 +1602,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>70</v>
-      </c>
-      <c r="G29" t="n">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1640,38 +1640,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1022</v>
-      </c>
-      <c r="G30" t="n">
-        <v>78</v>
+        <v>511</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1681,40 +1683,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>762</v>
+      </c>
+      <c r="G31" t="n">
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1724,40 +1724,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>512</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>528</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1765,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1782,23 +1780,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>718</v>
+        <v>62</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1808,38 +1806,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="G34" t="n">
-        <v>528</v>
+        <v>89</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1849,38 +1847,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>528</v>
+        <v>99</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1890,38 +1888,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1931,38 +1929,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1975,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1991,19 +1989,21 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" t="n">
-        <v>70</v>
+        <v>225</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2013,38 +2013,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>203</v>
       </c>
       <c r="G39" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -2054,40 +2054,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>227</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>411</v>
+      </c>
+      <c r="G40" t="n">
+        <v>248</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2100,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2116,19 +2114,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>197</v>
+        <v>33</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -2138,118 +2136,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>342</v>
+        <v>32</v>
       </c>
       <c r="G42" t="n">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>25</v>
-      </c>
-      <c r="G43" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>黄姑山路51-4号 0101park</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>16</v>
-      </c>
-      <c r="G44" t="n">
-        <v>68</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2421,7 +2337,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2503,7 +2419,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2767,7 +2683,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2867,7 +2783,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2894,33 +2810,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>富阳·原神&amp;崩铁&amp;崩坏only</t>
+          <t>杭州·AP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金桥北路与横凉亭路交叉口西北角 东方茂购物中心</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 09:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
+        <v>9014</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3vmxW0TA1705548094855.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2867,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -2990,10 +2908,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3031,7 +2949,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="G6" t="n">
         <v>40</v>
@@ -3072,7 +2990,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -3113,7 +3031,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
         <v>52</v>
@@ -3154,7 +3072,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3197,7 +3115,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -3279,7 +3197,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3835</v>
+        <v>3975</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3320,7 +3238,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="G13" t="n">
         <v>138</v>
@@ -3361,7 +3279,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="G14" t="n">
         <v>19.9</v>
@@ -3443,7 +3361,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
         <v>388</v>
@@ -3484,7 +3402,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -3525,7 +3443,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -3607,7 +3525,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
         <v>388</v>
@@ -3648,7 +3566,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
         <v>70</v>
@@ -3689,7 +3607,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G22" t="n">
         <v>89</v>
@@ -3730,7 +3648,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3853,7 +3771,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1389</v>
+        <v>1431</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -3894,7 +3812,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -3935,7 +3853,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -4019,7 +3937,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G30" t="n">
         <v>88</v>
@@ -4060,7 +3978,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -4142,7 +4060,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -4183,7 +4101,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G34" t="n">
         <v>79</v>
@@ -4224,7 +4142,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -4265,7 +4183,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4308,7 +4226,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -4349,7 +4267,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
@@ -4390,7 +4308,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G39" t="n">
         <v>528</v>
@@ -4431,7 +4349,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G40" t="n">
         <v>89</v>
@@ -4472,7 +4390,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
         <v>99</v>
@@ -4513,7 +4431,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G42" t="n">
         <v>70</v>
@@ -4595,7 +4513,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G44" t="n">
         <v>75</v>
@@ -4636,7 +4554,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="G45" t="n">
         <v>248</v>
@@ -4677,7 +4595,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G46" t="n">
         <v>39.9</v>
@@ -4718,7 +4636,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9014</v>
+        <v>9027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -628,10 +628,12 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>838</v>
-      </c>
-      <c r="G5" t="n">
-        <v>100</v>
+        <v>842</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -669,7 +671,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="G6" t="n">
         <v>40</v>
@@ -710,7 +712,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -751,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
         <v>52</v>
@@ -792,7 +794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -835,7 +837,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -876,7 +878,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3975</v>
+        <v>4040</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -917,7 +919,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>138</v>
@@ -958,10 +960,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>19.9</v>
+        <v>59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -999,7 +1001,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1040,7 +1042,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -1122,7 +1124,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -1204,7 +1206,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
         <v>50</v>
@@ -1245,7 +1247,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1431</v>
+        <v>1462</v>
       </c>
       <c r="G20" t="n">
         <v>70</v>
@@ -1286,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1327,7 +1329,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1411,7 +1413,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G24" t="n">
         <v>88</v>
@@ -1452,7 +1454,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G25" t="n">
         <v>68</v>
@@ -1493,7 +1495,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1534,7 +1536,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G27" t="n">
         <v>79</v>
@@ -1575,7 +1577,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G28" t="n">
         <v>78</v>
@@ -1702,7 +1704,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1743,7 +1745,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G32" t="n">
         <v>528</v>
@@ -1784,7 +1786,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -1825,7 +1827,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1866,7 +1868,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -1989,7 +1991,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2032,7 +2034,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2073,7 +2075,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2114,7 +2116,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2155,7 +2157,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2255,7 +2257,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2337,7 +2339,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2419,7 +2421,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2460,7 +2462,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>90</v>
@@ -2683,7 +2685,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2783,7 +2785,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2824,7 +2826,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9014</v>
+        <v>9027</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2867,10 +2869,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2908,10 +2910,12 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>838</v>
-      </c>
-      <c r="G5" t="n">
-        <v>100</v>
+        <v>842</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2949,7 +2953,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="G6" t="n">
         <v>40</v>
@@ -2990,7 +2994,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -3031,7 +3035,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
         <v>52</v>
@@ -3072,7 +3076,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3115,7 +3119,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -3156,7 +3160,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>58</v>
@@ -3197,7 +3201,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3975</v>
+        <v>4040</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3238,7 +3242,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="G13" t="n">
         <v>138</v>
@@ -3279,10 +3283,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>19.9</v>
+        <v>59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3361,7 +3365,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
         <v>388</v>
@@ -3402,7 +3406,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -3443,7 +3447,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -3525,7 +3529,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
         <v>388</v>
@@ -3607,7 +3611,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G22" t="n">
         <v>89</v>
@@ -3689,7 +3693,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>90</v>
@@ -3730,7 +3734,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -3771,7 +3775,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1431</v>
+        <v>1462</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -3812,7 +3816,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -3853,7 +3857,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>508</v>
+        <v>541</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3937,7 +3941,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G30" t="n">
         <v>88</v>
@@ -3978,7 +3982,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -4060,7 +4064,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -4101,7 +4105,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G34" t="n">
         <v>79</v>
@@ -4142,7 +4146,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -4226,7 +4230,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -4267,7 +4271,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
@@ -4308,7 +4312,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G39" t="n">
         <v>528</v>
@@ -4349,7 +4353,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G40" t="n">
         <v>89</v>
@@ -4390,7 +4394,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>99</v>
@@ -4513,7 +4517,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G44" t="n">
         <v>75</v>
@@ -4554,7 +4558,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="G45" t="n">
         <v>248</v>
@@ -4595,7 +4599,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G46" t="n">
         <v>39.9</v>
@@ -4636,7 +4640,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9027</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>759</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,40 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·樱之弦世界动漫游戏博览会（取消）</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2699</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>147</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78232</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/ZynJSATH1699345668160.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -568,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>326</v>
+        <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,40 +605,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>842</v>
+        <v>391</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -652,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>744</v>
+        <v>926</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>140</v>
+        <v>4153</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -734,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -775,40 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>389</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>216</v>
+      </c>
+      <c r="G9" t="n">
+        <v>53.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -818,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>921</v>
+        <v>826</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -859,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4040</v>
+        <v>788</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -900,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -941,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -982,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>817</v>
+        <v>521</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>781</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1105,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>511</v>
+        <v>1493</v>
       </c>
       <c r="G17" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>1389</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>573</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1222,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1462</v>
-      </c>
-      <c r="G20" t="n">
-        <v>70</v>
+        <v>293</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,38 +1265,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1374</v>
+        <v>161</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1311,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1329,19 +1325,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>541</v>
+        <v>201</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1356,35 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>293</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>417</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1399,33 +1393,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="G24" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1440,33 +1434,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>187</v>
+        <v>1028</v>
       </c>
       <c r="G25" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1475,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1495,19 +1489,21 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>394</v>
-      </c>
-      <c r="G26" t="n">
-        <v>60</v>
+        <v>17</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1517,38 +1513,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>79</v>
+        <v>509</v>
       </c>
       <c r="G27" t="n">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1558,38 +1554,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1025</v>
+        <v>829</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1599,40 +1595,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>89</v>
+      </c>
+      <c r="G29" t="n">
+        <v>528</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1642,40 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>511</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="G30" t="n">
+        <v>528</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1685,38 +1677,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>791</v>
+        <v>139</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1726,38 +1718,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>528</v>
+        <v>99</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1767,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>528</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1808,38 +1800,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1849,38 +1841,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
-      </c>
-      <c r="G35" t="n">
-        <v>99</v>
+        <v>224</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1890,38 +1884,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="G36" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -1931,38 +1925,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>479</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>248</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -1972,40 +1966,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>224</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="G38" t="n">
+        <v>39.9</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -2015,159 +2007,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>210</v>
+        <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>433</v>
-      </c>
-      <c r="G40" t="n">
-        <v>248</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>36</v>
-      </c>
-      <c r="G41" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>黄姑山路51-4号 0101park</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>34</v>
-      </c>
-      <c r="G42" t="n">
-        <v>68</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2257,7 +2126,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2339,7 +2208,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2421,7 +2290,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2585,7 +2454,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>120</v>
@@ -2685,7 +2554,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2785,7 +2654,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2807,40 +2676,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·AP动漫游戏嘉年华</t>
+          <t>杭州·动漫迷城嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>体育场路武林广场11号 杭州大厦中央商城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.03 09:00-02.04 17:00</t>
+          <t>2024.02.05 10:00-02.05 20:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9027</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>759</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79837</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/Fw2o6b8G1702608399635.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
         </is>
       </c>
     </row>
@@ -2850,38 +2717,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>富阳·原X铁X崩ONLY</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金桥北路1号 富阳东方茂</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 10:30-02.04 16:30</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>326</v>
+        <v>147</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80711</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Py42pqWv1704876608125.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -2891,40 +2758,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·偶像梦幻祭ONLY</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>石祥路242号 首开公园</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 10:00-02.04 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>842</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>89</v>
+      </c>
+      <c r="G5" t="n">
+        <v>52</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77815</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/NvdrSehn1698391117573.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -2934,38 +2799,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>744</v>
-      </c>
-      <c r="G6" t="n">
-        <v>40</v>
+        <v>391</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -2975,38 +2842,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>140</v>
+        <v>926</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3016,38 +2883,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3057,40 +2924,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>389</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>4153</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3100,38 +2965,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>921</v>
+        <v>336</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3141,38 +3006,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>53.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3182,38 +3047,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4040</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3223,38 +3088,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>321</v>
+        <v>115</v>
       </c>
       <c r="G13" t="n">
-        <v>138</v>
+        <v>388</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3264,38 +3129,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>200</v>
+        <v>826</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3310,33 +3175,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>788</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3346,38 +3211,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>388</v>
+        <v>180</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3387,38 +3252,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>817</v>
+        <v>85</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>388</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3428,38 +3293,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>781</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3469,38 +3334,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3510,38 +3375,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>521</v>
       </c>
       <c r="G20" t="n">
-        <v>388</v>
+        <v>89</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3551,38 +3416,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3592,38 +3457,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>511</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3633,38 +3498,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3674,38 +3539,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1493</v>
       </c>
       <c r="G24" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3720,33 +3585,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>1389</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3756,38 +3621,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1462</v>
+        <v>573</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3797,38 +3662,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1374</v>
-      </c>
-      <c r="G27" t="n">
-        <v>65</v>
+        <v>293</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3843,33 +3710,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>541</v>
+        <v>161</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3884,35 +3751,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>293</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>201</v>
+      </c>
+      <c r="G29" t="n">
+        <v>68</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3927,33 +3792,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3968,33 +3833,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>187</v>
+        <v>417</v>
       </c>
       <c r="G31" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -4009,33 +3874,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G32" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -4050,33 +3915,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>394</v>
+        <v>1028</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4091,33 +3956,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>79</v>
-      </c>
-      <c r="G34" t="n">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -4127,38 +3994,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1025</v>
+        <v>509</v>
       </c>
       <c r="G35" t="n">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4168,40 +4035,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>511</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>829</v>
+      </c>
+      <c r="G36" t="n">
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4081,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4226,23 +4091,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>791</v>
+        <v>89</v>
       </c>
       <c r="G37" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4117,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4267,23 +4132,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4293,38 +4158,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="G39" t="n">
-        <v>528</v>
+        <v>89</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4339,12 +4204,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4353,19 +4218,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4375,38 +4240,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G41" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4286,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4435,19 +4300,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4462,12 +4327,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4476,19 +4341,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
-        <v>55</v>
+        <v>224</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4384,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="G44" t="n">
         <v>75</v>
@@ -4558,7 +4425,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>433</v>
+        <v>479</v>
       </c>
       <c r="G45" t="n">
         <v>248</v>
@@ -4599,7 +4466,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G46" t="n">
         <v>39.9</v>
@@ -4640,7 +4507,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>
@@ -4722,7 +4589,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>120</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4153</v>
+        <v>4505</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>216</v>
+        <v>500</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="G10" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G11" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G14" t="n">
         <v>89</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1493</v>
+        <v>1519</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1532,10 +1532,12 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>509</v>
-      </c>
-      <c r="G27" t="n">
-        <v>218</v>
+        <v>521</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1573,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1614,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1655,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1696,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G31" t="n">
         <v>89</v>
@@ -1860,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1903,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1944,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="G37" t="n">
         <v>248</v>
@@ -1985,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G38" t="n">
         <v>39.9</v>
@@ -2208,7 +2210,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2290,7 +2292,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2331,7 +2333,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>90</v>
@@ -2554,7 +2556,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2654,7 +2656,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2695,10 +2697,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2736,7 +2738,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G4" t="n">
         <v>88</v>
@@ -2818,7 +2820,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2861,7 +2863,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -2943,7 +2945,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4153</v>
+        <v>4507</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -2984,7 +2986,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="G10" t="n">
         <v>138</v>
@@ -3025,7 +3027,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>216</v>
+        <v>501</v>
       </c>
       <c r="G11" t="n">
         <v>53.1</v>
@@ -3107,7 +3109,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G13" t="n">
         <v>388</v>
@@ -3148,7 +3150,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -3189,7 +3191,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -3271,7 +3273,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G17" t="n">
         <v>388</v>
@@ -3312,7 +3314,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
         <v>70</v>
@@ -3353,7 +3355,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
         <v>58</v>
@@ -3394,7 +3396,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G20" t="n">
         <v>89</v>
@@ -3476,7 +3478,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>90</v>
@@ -3558,7 +3560,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1493</v>
+        <v>1519</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -3599,7 +3601,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="G25" t="n">
         <v>65</v>
@@ -3640,7 +3642,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3681,7 +3683,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3724,7 +3726,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G28" t="n">
         <v>88</v>
@@ -3765,7 +3767,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="G29" t="n">
         <v>68</v>
@@ -3847,7 +3849,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3888,7 +3890,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G32" t="n">
         <v>79</v>
@@ -3929,7 +3931,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="G33" t="n">
         <v>78</v>
@@ -3970,7 +3972,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4013,10 +4015,12 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>509</v>
-      </c>
-      <c r="G35" t="n">
-        <v>218</v>
+        <v>521</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4054,7 +4058,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4095,7 +4099,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G37" t="n">
         <v>528</v>
@@ -4136,7 +4140,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G38" t="n">
         <v>528</v>
@@ -4177,7 +4181,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G39" t="n">
         <v>89</v>
@@ -4341,7 +4345,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4384,7 +4388,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="G44" t="n">
         <v>75</v>
@@ -4425,7 +4429,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="G45" t="n">
         <v>248</v>
@@ -4466,7 +4470,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G46" t="n">
         <v>39.9</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>764</v>
+        <v>161</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -528,33 +528,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>89</v>
-      </c>
-      <c r="G4" t="n">
-        <v>52</v>
+        <v>394</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,35 +612,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>394</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>936</v>
+      </c>
+      <c r="G5" t="n">
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>930</v>
+        <v>4826</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4505</v>
+        <v>364</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>347</v>
+        <v>548</v>
       </c>
       <c r="G8" t="n">
-        <v>138</v>
+        <v>53.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -771,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>844</v>
       </c>
       <c r="G9" t="n">
-        <v>53.1</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>837</v>
+        <v>795</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>790</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -899,33 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>531</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>525</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>1549</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1519</v>
+        <v>1414</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1398</v>
+        <v>656</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1196,23 +1196,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>602</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
+        <v>295</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,35 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>295</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>164</v>
+      </c>
+      <c r="G20" t="n">
+        <v>88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>214</v>
+        <v>445</v>
       </c>
       <c r="G22" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,33 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>427</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,33 +1393,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>88</v>
+        <v>1034</v>
       </c>
       <c r="G24" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1434,33 +1434,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1030</v>
-      </c>
-      <c r="G25" t="n">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1470,40 +1472,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>520</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1513,40 +1515,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>521</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1236</v>
+      </c>
+      <c r="G27" t="n">
+        <v>75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1571,23 +1571,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>853</v>
+        <v>120</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1612,23 +1612,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1638,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>528</v>
+        <v>29.9</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="G31" t="n">
         <v>89</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>99</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G33" t="n">
         <v>70</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="G37" t="n">
         <v>248</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G38" t="n">
         <v>39.9</v>
@@ -2009,36 +2009,118 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>杭州·赛马娘only—晴空雏菊</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.04.13 09:00-04.13 18:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>80</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.20 09:00-04.20 22:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>60</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>39</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F41" t="n">
+        <v>42</v>
+      </c>
+      <c r="G41" t="n">
         <v>68</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2210,7 +2292,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2292,7 +2374,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2556,7 +2638,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2656,7 +2738,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2678,38 +2760,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·动漫迷城嘉年华</t>
+          <t>杭州·小情侣only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>体育场路武林广场11号 杭州大厦中央商城</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.05 10:00-02.05 20:00</t>
+          <t>2024.02.14 10:00-02.14 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>764</v>
+        <v>161</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80216</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hJ9czIvz1705910017193.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
         </is>
       </c>
     </row>
@@ -2724,33 +2806,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -2760,38 +2842,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
-      </c>
-      <c r="G5" t="n">
-        <v>52</v>
+        <v>394</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -2806,35 +2890,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>394</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>936</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -2844,38 +2926,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>930</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2890,33 +2972,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>4826</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -2931,7 +3013,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2945,19 +3027,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4507</v>
+        <v>364</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -2967,38 +3049,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>347</v>
+        <v>548</v>
       </c>
       <c r="G10" t="n">
-        <v>138</v>
+        <v>53.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3008,38 +3090,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>501</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>53.1</v>
+        <v>90</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3054,33 +3136,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3095,33 +3177,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>119</v>
+        <v>844</v>
       </c>
       <c r="G13" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,33 +3218,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>837</v>
+        <v>795</v>
       </c>
       <c r="G14" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3172,38 +3254,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>790</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3218,33 +3300,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3336,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3300,33 +3382,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,33 +3423,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>531</v>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3377,38 +3459,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>525</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3418,38 +3500,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3459,38 +3541,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3505,33 +3587,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>1549</v>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
         </is>
       </c>
     </row>
@@ -3546,12 +3628,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3560,19 +3642,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1519</v>
+        <v>1414</v>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3582,38 +3664,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1398</v>
+        <v>656</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3710,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3638,23 +3720,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>602</v>
-      </c>
-      <c r="G26" t="n">
-        <v>60</v>
+        <v>295</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3669,35 +3753,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>295</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>164</v>
+      </c>
+      <c r="G27" t="n">
+        <v>88</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3712,33 +3794,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="G28" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3753,33 +3835,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3794,33 +3876,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="G30" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3835,33 +3917,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>427</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3876,33 +3958,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>88</v>
+        <v>1034</v>
       </c>
       <c r="G32" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3912,38 +3994,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1030</v>
-      </c>
-      <c r="G33" t="n">
-        <v>78</v>
+        <v>520</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3953,40 +4037,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1236</v>
+      </c>
+      <c r="G34" t="n">
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -3996,40 +4078,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>521</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="G35" t="n">
+        <v>528</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4119,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4054,23 +4134,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>853</v>
+        <v>69</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4080,38 +4160,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>528</v>
+        <v>29.9</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4121,38 +4201,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="G38" t="n">
-        <v>528</v>
+        <v>89</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4247,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4181,19 +4261,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4203,38 +4283,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="G40" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4329,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4263,19 +4343,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4285,38 +4365,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>242</v>
       </c>
       <c r="G42" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4326,40 +4406,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>226</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>528</v>
+      </c>
+      <c r="G43" t="n">
+        <v>248</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4452,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4388,19 +4466,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="G44" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4410,38 +4488,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>492</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -4451,38 +4529,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 09:00-04.20 22:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4589,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4826</v>
+        <v>4888</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1549</v>
+        <v>1578</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G20" t="n">
         <v>88</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G21" t="n">
         <v>68</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G23" t="n">
         <v>79</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1236</v>
+        <v>1426</v>
       </c>
       <c r="G27" t="n">
         <v>75</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G28" t="n">
         <v>528</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>29.9</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G31" t="n">
         <v>89</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>99</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G37" t="n">
         <v>248</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G38" t="n">
         <v>39.9</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>80</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
         <v>60</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G41" t="n">
         <v>68</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4826</v>
+        <v>4888</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="G9" t="n">
         <v>138</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G10" t="n">
         <v>53.1</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
         <v>388</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G16" t="n">
         <v>388</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
         <v>58</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1549</v>
+        <v>1579</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G31" t="n">
         <v>79</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G32" t="n">
         <v>78</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1236</v>
+        <v>1426</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G36" t="n">
         <v>528</v>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>80</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4888</v>
+        <v>4977</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1578</v>
+        <v>1626</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G20" t="n">
         <v>88</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="G21" t="n">
         <v>68</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G23" t="n">
         <v>79</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1426</v>
+        <v>1823</v>
       </c>
       <c r="G27" t="n">
         <v>75</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G28" t="n">
         <v>528</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
         <v>29.9</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="G31" t="n">
         <v>89</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
         <v>99</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G33" t="n">
         <v>70</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>55</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="G37" t="n">
         <v>248</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G38" t="n">
         <v>39.9</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G39" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G40" t="n">
         <v>60</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>90</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4888</v>
+        <v>4977</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="G9" t="n">
         <v>138</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="G10" t="n">
         <v>53.1</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G12" t="n">
         <v>388</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
         <v>388</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>58</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
         <v>90</v>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>飞虹路3号 杭州奥体中心综合训练馆</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1579</v>
+        <v>1626</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LpUZjVtC1705906700274.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G31" t="n">
         <v>79</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="G32" t="n">
         <v>78</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1426</v>
+        <v>1823</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G36" t="n">
         <v>528</v>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G40" t="n">
         <v>70</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4977</v>
+        <v>5032</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1626</v>
+        <v>1649</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1426</v>
+        <v>1431</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G20" t="n">
         <v>88</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="G21" t="n">
         <v>68</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G23" t="n">
         <v>79</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1823</v>
+        <v>2001</v>
       </c>
       <c r="G27" t="n">
         <v>75</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G28" t="n">
         <v>528</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
         <v>29.9</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G31" t="n">
         <v>89</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G33" t="n">
         <v>70</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="G37" t="n">
         <v>248</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G38" t="n">
         <v>39.9</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G39" t="n">
         <v>66</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G40" t="n">
         <v>60</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G41" t="n">
         <v>68</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>408</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
         <v>58</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4977</v>
+        <v>5032</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="G9" t="n">
         <v>138</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="G10" t="n">
         <v>53.1</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G12" t="n">
         <v>388</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="G13" t="n">
         <v>65</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" t="n">
         <v>388</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>58</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="G19" t="n">
         <v>89</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1626</v>
+        <v>1649</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1426</v>
+        <v>1431</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G31" t="n">
         <v>79</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="G32" t="n">
         <v>78</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1823</v>
+        <v>2001</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G36" t="n">
         <v>528</v>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G40" t="n">
         <v>70</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G45" t="n">
         <v>66</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
         <v>408</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5032</v>
+        <v>5100</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1649</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1431</v>
+        <v>1678</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>733</v>
+        <v>1433</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1196,25 +1196,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>295</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>763</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,33 +1227,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>177</v>
-      </c>
-      <c r="G20" t="n">
-        <v>88</v>
+        <v>295</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>267</v>
+        <v>180</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>475</v>
+        <v>284</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,33 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1393,33 +1393,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1041</v>
+        <v>122</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1434,35 +1434,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1041</v>
+      </c>
+      <c r="G25" t="n">
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1472,40 +1470,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>521</v>
+        <v>16</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1513,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>75</v>
+        <v>522</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1571,23 +1571,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>155</v>
+        <v>2223</v>
       </c>
       <c r="G28" t="n">
-        <v>528</v>
+        <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1612,23 +1612,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1638,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="G30" t="n">
-        <v>29.9</v>
+        <v>528</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1679,38 +1679,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>212</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -1725,33 +1725,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>99</v>
+        <v>29.9</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1761,38 +1761,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>38</v>
+        <v>226</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1802,38 +1802,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1862,21 +1862,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>226</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="G35" t="n">
+        <v>70</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1886,38 +1884,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1927,38 +1925,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>572</v>
-      </c>
-      <c r="G37" t="n">
-        <v>248</v>
+        <v>227</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1987,19 +1987,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>73</v>
+        <v>267</v>
       </c>
       <c r="G38" t="n">
-        <v>39.9</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -2009,38 +2009,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>29</v>
+        <v>593</v>
       </c>
       <c r="G39" t="n">
-        <v>66</v>
+        <v>248</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -2050,38 +2050,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>39.9</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -2091,36 +2091,118 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>杭州·赛马娘only—晴空雏菊</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.04.13 09:00-04.13 18:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>34</v>
+      </c>
+      <c r="G41" t="n">
+        <v>66</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.20 09:00-04.20 22:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>50</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F43" t="n">
+        <v>51</v>
+      </c>
+      <c r="G43" t="n">
         <v>68</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2292,7 +2374,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2374,7 +2456,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2638,7 +2720,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2738,7 +2820,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2779,7 +2861,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2820,7 +2902,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -2847,35 +2929,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>399</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>951</v>
+      </c>
+      <c r="G5" t="n">
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -2885,38 +2965,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>946</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2931,33 +3011,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>5100</v>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -2972,7 +3052,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2986,19 +3066,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5032</v>
+        <v>414</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3008,38 +3088,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>401</v>
+        <v>590</v>
       </c>
       <c r="G9" t="n">
-        <v>138</v>
+        <v>53.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3049,38 +3129,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>578</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>53.1</v>
+        <v>90</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3095,33 +3175,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="G11" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,33 +3216,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>136</v>
+        <v>892</v>
       </c>
       <c r="G12" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3177,33 +3257,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>877</v>
+        <v>805</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3213,38 +3293,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>803</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3259,33 +3339,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3375,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,33 +3421,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3382,33 +3462,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>546</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3423,33 +3503,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>544</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3558,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3601,7 +3681,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1649</v>
+        <v>1678</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3642,7 +3722,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3683,7 +3763,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>733</v>
+        <v>763</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3767,7 +3847,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -3808,7 +3888,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -3890,7 +3970,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3931,7 +4011,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G31" t="n">
         <v>79</v>
@@ -4013,7 +4093,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4056,7 +4136,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2001</v>
+        <v>2223</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4097,7 +4177,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4138,7 +4218,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G36" t="n">
         <v>528</v>
@@ -4179,7 +4259,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4220,7 +4300,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4302,7 +4382,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G40" t="n">
         <v>70</v>
@@ -4343,7 +4423,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4384,7 +4464,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4425,7 +4505,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4466,7 +4546,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4507,7 +4587,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G45" t="n">
         <v>66</v>
@@ -4548,7 +4628,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -4589,7 +4669,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5100</v>
+        <v>5143</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1678</v>
+        <v>1700</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2223</v>
+        <v>2326</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" t="n">
         <v>29.9</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G33" t="n">
         <v>89</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
         <v>55</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="G39" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G41" t="n">
         <v>66</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G43" t="n">
         <v>68</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>120</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5100</v>
+        <v>5143</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1678</v>
+        <v>1700</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G27" t="n">
         <v>88</v>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G31" t="n">
         <v>79</v>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G32" t="n">
         <v>78</v>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2223</v>
+        <v>2326</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G36" t="n">
         <v>528</v>
@@ -4240,38 +4240,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G37" t="n">
-        <v>29.9</v>
+        <v>258</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -4286,33 +4286,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="G38" t="n">
-        <v>89</v>
+        <v>29.9</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4341,19 +4341,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>230</v>
       </c>
       <c r="G39" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4363,38 +4363,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4423,19 +4423,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4445,38 +4445,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>267</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4505,19 +4505,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>593</v>
+        <v>269</v>
       </c>
       <c r="G43" t="n">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4546,19 +4546,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>78</v>
+        <v>606</v>
       </c>
       <c r="G44" t="n">
-        <v>39.9</v>
+        <v>248</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4568,38 +4568,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="G45" t="n">
-        <v>66</v>
+        <v>39.9</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G47" t="n">
         <v>68</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>120</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5143</v>
+        <v>5200</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1700</v>
+        <v>1726</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2326</v>
+        <v>2454</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1694,23 +1694,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -1720,38 +1720,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="G32" t="n">
-        <v>29.9</v>
+        <v>258</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -1766,33 +1766,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>89</v>
+        <v>29.9</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1821,19 +1821,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>244</v>
       </c>
       <c r="G34" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1843,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1903,19 +1903,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1944,21 +1944,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>227</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1968,38 +1966,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>269</v>
-      </c>
-      <c r="G38" t="n">
-        <v>75</v>
+        <v>226</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2028,19 +2028,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>606</v>
+        <v>272</v>
       </c>
       <c r="G39" t="n">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2069,19 +2069,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>78</v>
+        <v>628</v>
       </c>
       <c r="G40" t="n">
-        <v>39.9</v>
+        <v>248</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -2091,38 +2091,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G41" t="n">
-        <v>66</v>
+        <v>39.9</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -2132,38 +2132,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -2178,31 +2178,72 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.04.20 09:00-04.20 22:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>40</v>
+      </c>
+      <c r="G43" t="n">
+        <v>60</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>54</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F44" t="n">
+        <v>56</v>
+      </c>
+      <c r="G44" t="n">
         <v>68</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2219,7 +2260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2456,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2560,38 +2601,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.04.21 19:30-04.21 21:20</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
         </is>
       </c>
     </row>
@@ -2601,36 +2642,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>金沙大道681号 金沙湖大剧院</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.04.27 19:30-04.27 21:30</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>408</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>120</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
@@ -2861,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2902,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -2943,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3025,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5143</v>
+        <v>5200</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3066,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3107,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3189,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3230,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3271,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3334,38 +3416,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="G15" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3380,33 +3462,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3421,33 +3503,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>556</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3462,33 +3544,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>550</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3498,38 +3580,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3539,38 +3621,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3580,38 +3662,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3626,33 +3708,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>1726</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3667,12 +3749,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3681,19 +3763,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1700</v>
+        <v>1443</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3703,38 +3785,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1437</v>
+        <v>806</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3831,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3759,23 +3841,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>786</v>
-      </c>
-      <c r="G25" t="n">
-        <v>60</v>
+        <v>294</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3790,35 +3874,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>295</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>183</v>
+      </c>
+      <c r="G26" t="n">
+        <v>88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3833,33 +3915,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3874,33 +3956,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3915,33 +3997,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="G29" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3956,33 +4038,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>493</v>
+        <v>128</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3997,33 +4079,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>123</v>
+        <v>1043</v>
       </c>
       <c r="G31" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4033,38 +4115,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1043</v>
-      </c>
-      <c r="G32" t="n">
-        <v>78</v>
+        <v>524</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4074,40 +4158,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>523</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>2454</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4204,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4132,23 +4214,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2326</v>
+        <v>168</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4240,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4173,23 +4255,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4204,33 +4286,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G36" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -4240,38 +4322,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4286,33 +4368,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="G38" t="n">
-        <v>29.9</v>
+        <v>89</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4409,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4341,19 +4423,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4363,38 +4445,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4491,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4423,19 +4505,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4445,38 +4527,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="G42" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4573,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4505,19 +4587,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>269</v>
+        <v>628</v>
       </c>
       <c r="G43" t="n">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4614,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4546,19 +4628,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="G44" t="n">
-        <v>248</v>
+        <v>39.9</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4568,38 +4650,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 09:00-04.20 22:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
         </is>
       </c>
     </row>
@@ -4614,33 +4696,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
       </c>
     </row>
@@ -4650,38 +4732,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
+          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>黄姑山路51-4号 0101park</t>
+          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
+          <t>2024.04.21 19:30-04.21 21:20</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
         </is>
       </c>
     </row>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5200</v>
+        <v>5231</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1726</v>
+        <v>1747</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2454</v>
+        <v>2520</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>120</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5200</v>
+        <v>5231</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3416,38 +3416,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>388</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3462,33 +3462,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3503,33 +3503,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>556</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3544,33 +3544,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>564</v>
       </c>
       <c r="G18" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3580,38 +3580,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3621,38 +3621,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3662,38 +3662,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3708,33 +3708,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1726</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3763,19 +3763,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1443</v>
+        <v>1747</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3785,38 +3785,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>806</v>
+        <v>1450</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3841,25 +3841,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>294</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>819</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3929,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4011,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4052,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4093,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4134,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4177,7 +4175,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2454</v>
+        <v>2520</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -4259,7 +4257,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4300,7 +4298,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4341,7 +4339,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4382,7 +4380,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4423,7 +4421,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4573,7 +4571,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4587,19 +4585,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="G43" t="n">
-        <v>248</v>
+        <v>39.9</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4609,38 +4607,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="G44" t="n">
-        <v>39.9</v>
+        <v>66</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4667,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4710,7 +4708,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>
@@ -4833,7 +4831,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
         <v>120</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5231</v>
+        <v>5282</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1747</v>
+        <v>1762</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2520</v>
+        <v>2594</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>90</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5231</v>
+        <v>5282</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
         <v>90</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1747</v>
+        <v>1762</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2520</v>
+        <v>2594</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G35" t="n">
         <v>528</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G44" t="n">
         <v>66</v>
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5282</v>
+        <v>5304</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1762</v>
+        <v>1775</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2594</v>
+        <v>2626</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5282</v>
+        <v>5304</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1762</v>
+        <v>1775</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4113,40 +4113,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>525</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>2626</v>
+      </c>
+      <c r="G32" t="n">
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4159,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4171,23 +4169,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2594</v>
+        <v>173</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4195,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4212,23 +4210,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4243,33 +4241,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="G35" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4339,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4380,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4544,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4571,7 +4569,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4585,19 +4583,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="G43" t="n">
-        <v>39.9</v>
+        <v>248</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4607,38 +4605,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="G44" t="n">
-        <v>66</v>
+        <v>39.9</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4708,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5304</v>
+        <v>5371</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1775</v>
+        <v>1791</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2626</v>
+        <v>2705</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5304</v>
+        <v>5371</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1775</v>
+        <v>1791</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2626</v>
+        <v>2705</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5371</v>
+        <v>5407</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1791</v>
+        <v>1804</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2705</v>
+        <v>2759</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5371</v>
+        <v>5407</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1791</v>
+        <v>1804</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2705</v>
+        <v>2759</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5407</v>
+        <v>5474</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1804</v>
+        <v>1825</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2759</v>
+        <v>2843</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>676</v>
+        <v>699</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>408</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5407</v>
+        <v>5474</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1804</v>
+        <v>1825</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1460</v>
+        <v>1465</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2759</v>
+        <v>2843</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>676</v>
+        <v>699</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
         <v>408</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5474</v>
+        <v>5503</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1825</v>
+        <v>1844</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2843</v>
+        <v>2895</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>408</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5474</v>
+        <v>5503</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1825</v>
+        <v>1844</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2843</v>
+        <v>2895</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G40" t="n">
         <v>70</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
         <v>408</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5503</v>
+        <v>5571</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1844</v>
+        <v>1866</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2895</v>
+        <v>2985</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5503</v>
+        <v>5571</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
         <v>58</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1844</v>
+        <v>1866</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2895</v>
+        <v>2985</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
         <v>70</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5571</v>
+        <v>5596</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1866</v>
+        <v>1885</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2985</v>
+        <v>3025</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5571</v>
+        <v>5596</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1866</v>
+        <v>1885</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2985</v>
+        <v>3025</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
         <v>52</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5596</v>
+        <v>5650</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1885</v>
+        <v>1906</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3025</v>
+        <v>3107</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G4" t="n">
         <v>52</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5596</v>
+        <v>5650</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="G8" t="n">
         <v>138</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="G9" t="n">
         <v>53.1</v>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G15" t="n">
         <v>388</v>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G18" t="n">
         <v>89</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
         <v>158</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1885</v>
+        <v>1906</v>
       </c>
       <c r="G23" t="n">
         <v>70</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3025</v>
+        <v>3107</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G44" t="n">
         <v>39.9</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>221</v>
-      </c>
-      <c r="G2" t="n">
-        <v>88</v>
+        <v>222</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -545,7 +547,7 @@
         <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -626,7 +628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -667,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5650</v>
+        <v>5678</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -708,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -749,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="G9" t="n">
         <v>65</v>
@@ -831,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -913,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
         <v>58</v>
@@ -954,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G13" t="n">
         <v>89</v>
@@ -995,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
         <v>158</v>
@@ -1118,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1906</v>
+        <v>1922</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -1159,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1284,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -1325,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="G22" t="n">
         <v>68</v>
@@ -1366,7 +1368,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -1575,7 +1577,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3107</v>
+        <v>3171</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1616,7 +1618,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G29" t="n">
         <v>528</v>
@@ -1657,7 +1659,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -1698,7 +1700,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -1739,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -1821,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -2028,7 +2030,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2069,7 +2071,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -2110,7 +2112,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -2151,7 +2153,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -2192,7 +2194,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -2233,7 +2235,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2415,7 +2417,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2497,7 +2499,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2929,33 +2931,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·恋爱告急动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>221</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
         </is>
       </c>
     </row>
@@ -2965,38 +2967,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>122</v>
+        <v>1014</v>
       </c>
       <c r="G4" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -3006,38 +3008,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1011</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -3052,33 +3054,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>5678</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3095,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3107,19 +3109,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5650</v>
+        <v>526</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3131,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>520</v>
+        <v>743</v>
       </c>
       <c r="G8" t="n">
-        <v>138</v>
+        <v>53.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3170,38 +3172,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>731</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>53.1</v>
+        <v>90</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3216,33 +3218,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>224</v>
       </c>
       <c r="G10" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3257,33 +3259,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>218</v>
+        <v>979</v>
       </c>
       <c r="G11" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3298,33 +3300,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>973</v>
+        <v>829</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3334,38 +3336,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>828</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3380,33 +3382,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="G14" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3416,38 +3418,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3462,33 +3464,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3503,33 +3505,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>596</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3544,33 +3546,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>594</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3580,38 +3582,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3621,38 +3623,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3662,38 +3664,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3708,33 +3710,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>1922</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3751,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3763,19 +3765,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1906</v>
+        <v>1493</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3785,38 +3787,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1487</v>
+        <v>986</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3831,33 +3833,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>970</v>
+        <v>201</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3872,33 +3874,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>199</v>
+        <v>359</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3913,33 +3915,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3954,33 +3956,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="G28" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3995,33 +3997,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>575</v>
+        <v>176</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -4036,33 +4038,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>168</v>
+        <v>1062</v>
       </c>
       <c r="G30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4072,38 +4074,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1062</v>
+        <v>3171</v>
       </c>
       <c r="G31" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4120,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4128,23 +4130,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3107</v>
+        <v>186</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4156,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4169,23 +4171,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4200,33 +4202,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="G34" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4243,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4251,23 +4253,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -4277,38 +4279,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="G36" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4323,33 +4325,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>41</v>
+        <v>433</v>
       </c>
       <c r="G37" t="n">
-        <v>29.9</v>
+        <v>89</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4366,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4378,19 +4380,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>424</v>
+        <v>15</v>
       </c>
       <c r="G38" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4400,38 +4402,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G39" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4448,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4460,19 +4462,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4482,38 +4484,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>16</v>
+        <v>306</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4530,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4542,19 +4544,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>304</v>
+        <v>764</v>
       </c>
       <c r="G42" t="n">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4571,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4583,19 +4585,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>754</v>
+        <v>97</v>
       </c>
       <c r="G43" t="n">
-        <v>248</v>
+        <v>39.9</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4605,38 +4607,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="G44" t="n">
-        <v>39.9</v>
+        <v>66</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4667,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4706,7 +4708,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·小情侣only</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 18:00</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>413</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81088</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/mg76jpu81705643322225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,38 +525,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>122</v>
+        <v>1022</v>
       </c>
       <c r="G3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,40 +566,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>409</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>5732</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1014</v>
+        <v>533</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,38 +648,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5678</v>
+        <v>771</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>53.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>526</v>
+        <v>998</v>
       </c>
       <c r="G7" t="n">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +730,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
+        <v>835</v>
       </c>
       <c r="G8" t="n">
-        <v>53.1</v>
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>979</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>829</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>600</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -896,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>596</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1019,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>1933</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -1060,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>1497</v>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1101,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1922</v>
+        <v>1006</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1142,38 +1140,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1493</v>
-      </c>
-      <c r="G18" t="n">
-        <v>65</v>
+        <v>300</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1183,38 +1183,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>986</v>
+        <v>203</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1224,40 +1224,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>299</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>368</v>
+      </c>
+      <c r="G20" t="n">
+        <v>68</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1267,17 +1265,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1286,19 +1284,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>201</v>
+        <v>597</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1308,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>359</v>
+        <v>206</v>
       </c>
       <c r="G22" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1349,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>580</v>
+        <v>1063</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1390,38 +1388,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>176</v>
-      </c>
-      <c r="G24" t="n">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1431,38 +1431,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1062</v>
-      </c>
-      <c r="G25" t="n">
-        <v>78</v>
+        <v>525</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1472,40 +1474,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3253</v>
+      </c>
+      <c r="G26" t="n">
+        <v>75</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,40 +1515,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>526</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>187</v>
+      </c>
+      <c r="G27" t="n">
+        <v>528</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1556,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1573,23 +1571,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3171</v>
+        <v>123</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1599,38 +1597,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="G29" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -1640,38 +1638,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G30" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -1681,38 +1679,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1722,38 +1720,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>138</v>
+        <v>444</v>
       </c>
       <c r="G32" t="n">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1763,38 +1761,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>29.9</v>
+        <v>99</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,38 +1802,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>433</v>
+        <v>44</v>
       </c>
       <c r="G34" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1845,38 +1843,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1886,17 +1884,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1905,19 +1903,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
-      </c>
-      <c r="G36" t="n">
-        <v>70</v>
+        <v>226</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1927,38 +1927,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>312</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -1968,40 +1968,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>226</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>779</v>
+      </c>
+      <c r="G38" t="n">
+        <v>248</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2009,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2030,19 +2028,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>306</v>
+        <v>98</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -2052,38 +2050,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>764</v>
+        <v>63</v>
       </c>
       <c r="G40" t="n">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -2093,38 +2091,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 09:00-04.20 22:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="G41" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
         </is>
       </c>
     </row>
@@ -2134,118 +2132,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G42" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>67</v>
-      </c>
-      <c r="G43" t="n">
-        <v>60</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>黄姑山路51-4号 0101park</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>74</v>
-      </c>
-      <c r="G44" t="n">
-        <v>68</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2316,7 +2232,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2357,7 +2273,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2398,7 +2314,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2417,7 +2333,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2439,7 +2355,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2480,7 +2396,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2499,7 +2415,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2521,7 +2437,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2562,7 +2478,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2603,7 +2519,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2644,7 +2560,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024.04.27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2685,7 +2601,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2785,7 +2701,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2023.12.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2885,7 +2801,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2023.12.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2926,38 +2842,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·恋爱告急动漫游戏展</t>
+          <t>杭州·PJSK only展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>望江东路333号 杭州瑞莱克斯大酒店</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 10:00-02.16 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>122</v>
-      </c>
-      <c r="G3" t="n">
-        <v>62</v>
+        <v>413</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/de0lsSbz1706180254353.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2885,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2986,7 +2904,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -3008,7 +2926,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3049,7 +2967,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3068,7 +2986,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5678</v>
+        <v>5732</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -3090,7 +3008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3109,7 +3027,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -3131,7 +3049,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3150,7 +3068,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -3172,7 +3090,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3213,7 +3131,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3232,7 +3150,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G10" t="n">
         <v>388</v>
@@ -3254,7 +3172,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3273,7 +3191,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>979</v>
+        <v>998</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -3295,7 +3213,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3314,7 +3232,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -3336,7 +3254,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3377,7 +3295,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3396,7 +3314,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G14" t="n">
         <v>388</v>
@@ -3418,7 +3336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3437,7 +3355,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -3459,7 +3377,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3478,7 +3396,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
         <v>58</v>
@@ -3500,7 +3418,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3519,7 +3437,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -3541,7 +3459,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3560,7 +3478,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
         <v>158</v>
@@ -3582,7 +3500,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3623,7 +3541,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3664,7 +3582,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3683,7 +3601,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -3705,7 +3623,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3724,7 +3642,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1922</v>
+        <v>1933</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -3746,7 +3664,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3765,7 +3683,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3787,7 +3705,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3806,7 +3724,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>986</v>
+        <v>1006</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3828,7 +3746,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3847,7 +3765,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G25" t="n">
         <v>88</v>
@@ -3869,7 +3787,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3888,7 +3806,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="G26" t="n">
         <v>68</v>
@@ -3910,7 +3828,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3951,7 +3869,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3970,7 +3888,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3992,7 +3910,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4011,7 +3929,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="G29" t="n">
         <v>79</v>
@@ -4033,7 +3951,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4052,7 +3970,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G30" t="n">
         <v>78</v>
@@ -4074,7 +3992,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4093,7 +4011,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3171</v>
+        <v>3253</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -4115,7 +4033,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4134,7 +4052,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G32" t="n">
         <v>528</v>
@@ -4156,7 +4074,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4175,7 +4093,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4197,7 +4115,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4216,7 +4134,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="G34" t="n">
         <v>258</v>
@@ -4238,7 +4156,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4257,7 +4175,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4279,7 +4197,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4298,7 +4216,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G36" t="n">
         <v>29.9</v>
@@ -4320,7 +4238,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4339,7 +4257,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="G37" t="n">
         <v>89</v>
@@ -4361,7 +4279,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4380,7 +4298,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38" t="n">
         <v>99</v>
@@ -4402,7 +4320,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4421,7 +4339,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G39" t="n">
         <v>70</v>
@@ -4443,7 +4361,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4462,7 +4380,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
         <v>55</v>
@@ -4484,7 +4402,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4503,7 +4421,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -4525,7 +4443,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4544,7 +4462,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="G42" t="n">
         <v>248</v>
@@ -4566,7 +4484,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4585,7 +4503,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G43" t="n">
         <v>39.9</v>
@@ -4607,7 +4525,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4626,7 +4544,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G44" t="n">
         <v>66</v>
@@ -4648,7 +4566,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4667,7 +4585,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4689,7 +4607,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4708,7 +4626,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>
@@ -4730,7 +4648,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4771,7 +4689,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024.04.27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4812,7 +4730,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5732</v>
+        <v>5764</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G5" t="n">
         <v>138</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>771</v>
+        <v>985</v>
       </c>
       <c r="G6" t="n">
         <v>53.1</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="G11" t="n">
         <v>89</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1933</v>
+        <v>1947</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1006</v>
+        <v>1028</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G19" t="n">
         <v>88</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="G20" t="n">
         <v>68</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G22" t="n">
         <v>79</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3253</v>
+        <v>3301</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G27" t="n">
         <v>528</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G28" t="n">
         <v>528</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
         <v>258</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G30" t="n">
         <v>258</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
         <v>29.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G32" t="n">
         <v>89</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" t="n">
         <v>55</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="G38" t="n">
         <v>248</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G39" t="n">
         <v>39.9</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G40" t="n">
         <v>66</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>180</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5732</v>
+        <v>5764</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>771</v>
+        <v>985</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="G10" t="n">
         <v>388</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>180</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G14" t="n">
         <v>388</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>58</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
         <v>158</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1933</v>
+        <v>1947</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1006</v>
+        <v>1028</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3751,33 +3751,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>203</v>
-      </c>
-      <c r="G25" t="n">
-        <v>88</v>
+        <v>301</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3792,33 +3794,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>368</v>
+        <v>205</v>
       </c>
       <c r="G26" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3833,33 +3835,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3874,33 +3876,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>597</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3915,33 +3917,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>206</v>
+        <v>600</v>
       </c>
       <c r="G29" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3956,33 +3958,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1063</v>
+        <v>211</v>
       </c>
       <c r="G30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3992,38 +3994,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3253</v>
+        <v>1064</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4040,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4048,23 +4050,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>187</v>
+        <v>3301</v>
       </c>
       <c r="G32" t="n">
-        <v>528</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4076,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4089,23 +4091,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4120,33 +4122,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="G34" t="n">
-        <v>258</v>
+        <v>528</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4163,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4171,23 +4173,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -4197,38 +4199,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="G36" t="n">
-        <v>29.9</v>
+        <v>258</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -4243,33 +4245,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>444</v>
+        <v>44</v>
       </c>
       <c r="G37" t="n">
-        <v>89</v>
+        <v>29.9</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4284,12 +4286,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4298,19 +4300,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>453</v>
       </c>
       <c r="G38" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4320,38 +4322,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4368,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4380,19 +4382,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G40" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4402,38 +4404,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>312</v>
+        <v>18</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4450,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4462,19 +4464,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>779</v>
+        <v>314</v>
       </c>
       <c r="G42" t="n">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4491,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4503,19 +4505,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>98</v>
+        <v>786</v>
       </c>
       <c r="G43" t="n">
-        <v>39.9</v>
+        <v>248</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4525,38 +4527,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="G44" t="n">
-        <v>66</v>
+        <v>39.9</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4587,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4626,7 +4628,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5764</v>
+        <v>5805</v>
       </c>
       <c r="G4" t="n">
         <v>65</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="G5" t="n">
         <v>138</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>985</v>
+        <v>1011</v>
       </c>
       <c r="G6" t="n">
         <v>53.1</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="G11" t="n">
         <v>89</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
         <v>158</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G19" t="n">
         <v>88</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G20" t="n">
         <v>68</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G22" t="n">
         <v>79</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3301</v>
+        <v>3417</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G27" t="n">
         <v>528</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G28" t="n">
         <v>528</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G30" t="n">
         <v>258</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G31" t="n">
         <v>29.9</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="G32" t="n">
         <v>89</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
         <v>99</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="G38" t="n">
         <v>248</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G40" t="n">
         <v>66</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>257</v>
+        <v>532</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
         <v>58</v>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5764</v>
+        <v>5805</v>
       </c>
       <c r="G6" t="n">
         <v>65</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="G7" t="n">
         <v>138</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>985</v>
+        <v>1011</v>
       </c>
       <c r="G8" t="n">
         <v>53.1</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>257</v>
+        <v>532</v>
       </c>
       <c r="G10" t="n">
         <v>388</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="G14" t="n">
         <v>388</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
         <v>58</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="G17" t="n">
         <v>89</v>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
         <v>158</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="G22" t="n">
         <v>70</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1028</v>
+        <v>1056</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" t="n">
         <v>88</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G27" t="n">
         <v>68</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G30" t="n">
         <v>79</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3301</v>
+        <v>3417</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G34" t="n">
         <v>528</v>
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G36" t="n">
         <v>258</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G37" t="n">
         <v>29.9</v>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
         <v>99</v>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="G43" t="n">
         <v>248</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5805</v>
+        <v>5826</v>
       </c>
       <c r="G4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G5" t="n">
         <v>138</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1011</v>
+        <v>1033</v>
       </c>
       <c r="G6" t="n">
         <v>53.1</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="G7" t="n">
         <v>65</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="G8" t="n">
         <v>50</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G11" t="n">
         <v>89</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
         <v>158</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1972</v>
+        <v>1986</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="G20" t="n">
         <v>68</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="G22" t="n">
         <v>79</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3417</v>
+        <v>3484</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G27" t="n">
         <v>528</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G28" t="n">
         <v>528</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G29" t="n">
         <v>258</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G30" t="n">
         <v>258</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="G32" t="n">
         <v>89</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
         <v>99</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
         <v>55</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>807</v>
+        <v>820</v>
       </c>
       <c r="G38" t="n">
         <v>248</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G39" t="n">
         <v>39.9</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G41" t="n">
         <v>60</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>532</v>
+        <v>591</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
         <v>408</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G2" t="n">
         <v>108</v>
@@ -2847,35 +2847,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第34届中二病动漫游戏展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.16 11:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>415</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1039</v>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
         </is>
       </c>
     </row>
@@ -2885,38 +2883,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1030</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2931,33 +2929,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>5826</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2970,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2986,19 +2984,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5805</v>
+        <v>543</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -3008,38 +3006,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>541</v>
+        <v>1033</v>
       </c>
       <c r="G7" t="n">
-        <v>138</v>
+        <v>53.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3049,38 +3047,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1011</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>53.1</v>
+        <v>90</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3095,33 +3093,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>591</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,33 +3134,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>532</v>
+        <v>1036</v>
       </c>
       <c r="G10" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3177,33 +3175,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1023</v>
+        <v>846</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3213,38 +3211,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>842</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3259,33 +3257,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>320</v>
       </c>
       <c r="G13" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3293,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>294</v>
+        <v>85</v>
       </c>
       <c r="G14" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,33 +3339,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3382,33 +3380,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>613</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3423,33 +3421,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>611</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3459,38 +3457,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3500,38 +3498,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3541,38 +3539,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3587,33 +3585,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>1986</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3626,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3642,19 +3640,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1972</v>
+        <v>1509</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3664,38 +3662,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1506</v>
+        <v>1067</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3708,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3720,23 +3718,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1056</v>
-      </c>
-      <c r="G24" t="n">
-        <v>60</v>
+        <v>303</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3751,35 +3751,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>301</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>206</v>
+      </c>
+      <c r="G25" t="n">
+        <v>88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3794,33 +3792,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>206</v>
+        <v>398</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3835,33 +3833,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3876,33 +3874,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>633</v>
       </c>
       <c r="G28" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3917,33 +3915,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>620</v>
+        <v>226</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3958,33 +3956,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>220</v>
+        <v>1070</v>
       </c>
       <c r="G30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3994,38 +3992,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1067</v>
+        <v>3484</v>
       </c>
       <c r="G31" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4038,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4050,23 +4048,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3417</v>
+        <v>192</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4074,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4091,23 +4089,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -4122,33 +4120,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G34" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4161,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4173,23 +4171,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -4199,38 +4197,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="G36" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4245,33 +4243,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>49</v>
+        <v>488</v>
       </c>
       <c r="G37" t="n">
-        <v>29.9</v>
+        <v>89</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4284,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4300,19 +4298,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>478</v>
+        <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4322,38 +4320,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G39" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4366,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4382,19 +4380,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4404,38 +4402,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4448,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4464,19 +4462,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>316</v>
+        <v>820</v>
       </c>
       <c r="G42" t="n">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4489,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4505,19 +4503,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>807</v>
+        <v>103</v>
       </c>
       <c r="G43" t="n">
-        <v>248</v>
+        <v>39.9</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4527,38 +4525,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="G44" t="n">
-        <v>39.9</v>
+        <v>66</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4585,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4628,7 +4626,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>
@@ -4710,7 +4708,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G48" t="n">
         <v>408</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·PJSK only展</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 18:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>416</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>5880</v>
+      </c>
+      <c r="G2" t="n">
+        <v>98</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80124</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/JAPoQ5pq1703226277836.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1039</v>
+        <v>554</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -566,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5826</v>
+        <v>1064</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>543</v>
+        <v>1045</v>
       </c>
       <c r="G5" t="n">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1033</v>
+        <v>852</v>
       </c>
       <c r="G6" t="n">
-        <v>53.1</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -689,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1036</v>
+        <v>86</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>846</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>613</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>2018</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>1514</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1986</v>
+        <v>1101</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1509</v>
+        <v>303</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1102,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1067</v>
+        <v>209</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,35 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>303</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>414</v>
+      </c>
+      <c r="G18" t="n">
+        <v>68</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1184,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1202,19 +1198,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>206</v>
+        <v>646</v>
       </c>
       <c r="G19" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>398</v>
+        <v>232</v>
       </c>
       <c r="G20" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1266,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>633</v>
+        <v>1072</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1311,33 +1307,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>226</v>
-      </c>
-      <c r="G22" t="n">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1345,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1070</v>
-      </c>
-      <c r="G23" t="n">
-        <v>78</v>
+        <v>527</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,40 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3604</v>
+      </c>
+      <c r="G24" t="n">
+        <v>75</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1431,40 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>527</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>196</v>
+      </c>
+      <c r="G25" t="n">
+        <v>528</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1489,23 +1485,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3484</v>
+        <v>133</v>
       </c>
       <c r="G26" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1511,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="G27" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -1561,33 +1557,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="G28" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -1597,38 +1593,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>157</v>
+        <v>509</v>
       </c>
       <c r="G30" t="n">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1684,33 +1680,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>29.9</v>
+        <v>99</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1720,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>488</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1761,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G33" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1803,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1821,19 +1817,21 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>49</v>
-      </c>
-      <c r="G34" t="n">
-        <v>70</v>
+        <v>228</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1841,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="G35" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -1884,40 +1882,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>228</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>840</v>
+      </c>
+      <c r="G36" t="n">
+        <v>248</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1928,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1946,19 +1942,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>319</v>
+        <v>106</v>
       </c>
       <c r="G37" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -1968,38 +1964,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>820</v>
+        <v>72</v>
       </c>
       <c r="G38" t="n">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -2009,38 +2005,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 09:00-04.20 22:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="G39" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
         </is>
       </c>
     </row>
@@ -2050,118 +2046,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="G40" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>78</v>
-      </c>
-      <c r="G41" t="n">
-        <v>60</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>黄姑山路51-4号 0101park</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>86</v>
-      </c>
-      <c r="G42" t="n">
-        <v>68</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2251,7 +2165,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
         <v>58</v>
@@ -2333,7 +2247,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>591</v>
+        <v>749</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2415,7 +2329,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>320</v>
+        <v>411</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2620,7 +2534,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>120</v>
@@ -2722,8 +2636,10 @@
       <c r="F2" t="n">
         <v>239</v>
       </c>
-      <c r="G2" t="n">
-        <v>108</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2822,8 +2738,10 @@
       <c r="F2" t="n">
         <v>239</v>
       </c>
-      <c r="G2" t="n">
-        <v>108</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2842,38 +2760,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·第34届中二病动漫游戏展</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1039</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79971</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/FrKjHyyu1702971763457.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2888,33 +2806,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>5880</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2847,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2943,19 +2861,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5826</v>
+        <v>554</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -2965,38 +2883,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>543</v>
+        <v>1064</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -3006,38 +2924,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1033</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>53.1</v>
+        <v>90</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -3052,33 +2970,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>749</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -3093,33 +3011,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>591</v>
+        <v>1045</v>
       </c>
       <c r="G9" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3134,33 +3052,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1036</v>
+        <v>852</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3170,38 +3088,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>846</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3216,33 +3134,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>411</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3252,38 +3170,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>320</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3298,33 +3216,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3339,33 +3257,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>615</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3380,33 +3298,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>613</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3416,38 +3334,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3457,38 +3375,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3498,38 +3416,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3544,33 +3462,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>2018</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3503,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3599,19 +3517,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1986</v>
+        <v>1514</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3621,38 +3539,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1509</v>
+        <v>1101</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3585,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3677,23 +3595,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1067</v>
+        <v>303</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3708,35 +3626,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>303</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>209</v>
+      </c>
+      <c r="G24" t="n">
+        <v>88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3751,33 +3667,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>206</v>
+        <v>414</v>
       </c>
       <c r="G25" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3792,33 +3708,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3833,33 +3749,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3874,33 +3790,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>633</v>
+        <v>232</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3915,33 +3831,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>226</v>
+        <v>1072</v>
       </c>
       <c r="G29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3951,38 +3867,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1070</v>
-      </c>
-      <c r="G30" t="n">
-        <v>78</v>
+        <v>527</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -4011,7 +3929,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3484</v>
+        <v>3605</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -4052,7 +3970,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G32" t="n">
         <v>528</v>
@@ -4093,7 +4011,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G33" t="n">
         <v>528</v>
@@ -4134,7 +4052,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G34" t="n">
         <v>258</v>
@@ -4175,7 +4093,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G35" t="n">
         <v>258</v>
@@ -4216,7 +4134,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G36" t="n">
         <v>29.9</v>
@@ -4257,7 +4175,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="G37" t="n">
         <v>89</v>
@@ -4339,7 +4257,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G39" t="n">
         <v>70</v>
@@ -4380,7 +4298,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G40" t="n">
         <v>55</v>
@@ -4421,7 +4339,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -4462,7 +4380,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="G42" t="n">
         <v>248</v>
@@ -4503,7 +4421,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G43" t="n">
         <v>39.9</v>
@@ -4544,7 +4462,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G44" t="n">
         <v>66</v>
@@ -4585,7 +4503,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4626,7 +4544,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>
@@ -4749,7 +4667,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>120</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5880</v>
+        <v>5901</v>
       </c>
       <c r="G2" t="n">
         <v>98</v>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G3" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1064</v>
+        <v>1089</v>
       </c>
       <c r="G4" t="n">
         <v>59</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G9" t="n">
         <v>89</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2018</v>
+        <v>2042</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1101</v>
+        <v>1120</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,10 +1075,12 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>303</v>
-      </c>
-      <c r="G16" t="n">
-        <v>218</v>
+        <v>306</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1157,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="G18" t="n">
         <v>68</v>
@@ -1198,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1239,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G20" t="n">
         <v>79</v>
@@ -1364,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1407,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3604</v>
+        <v>3693</v>
       </c>
       <c r="G24" t="n">
         <v>75</v>
@@ -1448,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G25" t="n">
         <v>528</v>
@@ -1489,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G26" t="n">
         <v>528</v>
@@ -1530,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G27" t="n">
         <v>258</v>
@@ -1571,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G28" t="n">
         <v>258</v>
@@ -1612,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
         <v>29.9</v>
@@ -1653,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="G30" t="n">
         <v>89</v>
@@ -1735,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -1776,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -1860,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -1901,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="G36" t="n">
         <v>248</v>
@@ -2024,7 +2026,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2065,7 +2067,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -2168,7 +2170,7 @@
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2247,7 +2249,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2329,7 +2331,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2561,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2606,49 +2608,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2023.12.30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>杭州·伊藤润二官方快闪店 限定特典礼包</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>新业路228号 杭州来福士中心</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2023.12.30 10:00-2024.02.16 22:00</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>239</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80137</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TRE8uUjw1703229665251.png</t>
         </is>
       </c>
     </row>
@@ -2717,40 +2676,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023.12.30</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·伊藤润二官方快闪店 限定特典礼包</t>
+          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新业路228号 杭州来福士中心</t>
+          <t>同协路288号 1928创意园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2023.12.30 10:00-2024.02.16 22:00</t>
+          <t>2024.02.17 10:00-02.17 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>239</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="G2" t="n">
+        <v>68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80137</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/TRE8uUjw1703229665251.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
         </is>
       </c>
     </row>
@@ -2765,33 +2722,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>5901</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2763,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2820,19 +2777,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5880</v>
+        <v>556</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -2842,38 +2799,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>554</v>
+        <v>1089</v>
       </c>
       <c r="G5" t="n">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -2883,38 +2840,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1064</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2929,33 +2886,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>754</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -2970,33 +2927,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>749</v>
+        <v>1051</v>
       </c>
       <c r="G8" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -3011,33 +2968,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1045</v>
+        <v>853</v>
       </c>
       <c r="G9" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -3047,38 +3004,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>852</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3093,33 +3050,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>415</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3129,38 +3086,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>411</v>
+        <v>88</v>
       </c>
       <c r="G12" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3175,33 +3132,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3216,33 +3173,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>616</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3257,33 +3214,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>615</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3293,38 +3250,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3334,38 +3291,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3375,38 +3332,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3421,33 +3378,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>2042</v>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3419,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3476,19 +3433,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2018</v>
+        <v>1523</v>
       </c>
       <c r="G20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3498,38 +3455,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1514</v>
+        <v>1120</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3501,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3554,23 +3511,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1101</v>
-      </c>
-      <c r="G22" t="n">
-        <v>60</v>
+        <v>306</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3585,33 +3544,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>303</v>
+        <v>209</v>
       </c>
       <c r="G23" t="n">
-        <v>218</v>
+        <v>88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3626,33 +3585,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>209</v>
+        <v>429</v>
       </c>
       <c r="G24" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3667,33 +3626,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3708,33 +3667,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="G26" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3749,33 +3708,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>646</v>
+        <v>234</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3790,33 +3749,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>232</v>
+        <v>1072</v>
       </c>
       <c r="G28" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3826,38 +3785,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1072</v>
-      </c>
-      <c r="G29" t="n">
-        <v>78</v>
+        <v>528</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3867,40 +3828,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>527</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>3693</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3874,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3925,23 +3884,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3605</v>
+        <v>199</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -3951,12 +3910,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3966,23 +3925,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="G32" t="n">
         <v>528</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3997,33 +3956,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="G33" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -4038,7 +3997,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4048,23 +4007,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="G34" t="n">
         <v>258</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -4074,38 +4033,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="G35" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4120,33 +4079,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>51</v>
+        <v>524</v>
       </c>
       <c r="G36" t="n">
-        <v>29.9</v>
+        <v>89</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4161,12 +4120,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4175,19 +4134,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>509</v>
+        <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4197,38 +4156,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G38" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4202,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4257,19 +4216,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4284,12 +4243,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4298,19 +4257,21 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
-      </c>
-      <c r="G40" t="n">
-        <v>55</v>
+        <v>228</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4300,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -4380,7 +4341,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="G42" t="n">
         <v>248</v>
@@ -4503,7 +4464,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4544,7 +4505,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5901</v>
+        <v>5924</v>
       </c>
       <c r="G2" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="G3" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1089</v>
+        <v>1124</v>
       </c>
       <c r="G4" t="n">
         <v>59</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1051</v>
+        <v>1067</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G9" t="n">
         <v>89</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2042</v>
+        <v>2086</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1120</v>
+        <v>1155</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G17" t="n">
         <v>88</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="G18" t="n">
         <v>68</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>652</v>
+        <v>674</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G20" t="n">
         <v>79</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="G21" t="n">
         <v>78</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3693</v>
+        <v>3800</v>
       </c>
       <c r="G24" t="n">
         <v>75</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G25" t="n">
         <v>528</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G27" t="n">
         <v>258</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G28" t="n">
         <v>258</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" t="n">
         <v>29.9</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="G30" t="n">
         <v>89</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="G36" t="n">
         <v>248</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G37" t="n">
         <v>39.9</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G38" t="n">
         <v>66</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -2169,8 +2169,10 @@
       <c r="F2" t="n">
         <v>36</v>
       </c>
-      <c r="G2" t="n">
-        <v>68</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2249,7 +2251,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2331,7 +2333,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G6" t="n">
         <v>388</v>
@@ -2697,8 +2699,10 @@
       <c r="F2" t="n">
         <v>36</v>
       </c>
-      <c r="G2" t="n">
-        <v>68</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已停售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2736,10 +2740,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5901</v>
+        <v>5924</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2777,10 +2781,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="G4" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2818,7 +2822,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1089</v>
+        <v>1124</v>
       </c>
       <c r="G5" t="n">
         <v>59</v>
@@ -2900,7 +2904,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="G7" t="n">
         <v>388</v>
@@ -2941,7 +2945,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1051</v>
+        <v>1067</v>
       </c>
       <c r="G8" t="n">
         <v>65</v>
@@ -2982,7 +2986,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="G9" t="n">
         <v>50</v>
@@ -3064,7 +3068,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G11" t="n">
         <v>388</v>
@@ -3105,7 +3109,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G12" t="n">
         <v>70</v>
@@ -3146,7 +3150,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -3187,7 +3191,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G14" t="n">
         <v>89</v>
@@ -3228,7 +3232,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
         <v>158</v>
@@ -3269,7 +3273,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3351,7 +3355,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -3392,7 +3396,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2042</v>
+        <v>2086</v>
       </c>
       <c r="G19" t="n">
         <v>70</v>
@@ -3433,7 +3437,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3474,7 +3478,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1120</v>
+        <v>1155</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3515,7 +3519,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3558,7 +3562,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G23" t="n">
         <v>88</v>
@@ -3599,7 +3603,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="G24" t="n">
         <v>68</v>
@@ -3681,7 +3685,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>652</v>
+        <v>674</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3722,7 +3726,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G27" t="n">
         <v>79</v>
@@ -3763,7 +3767,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="G28" t="n">
         <v>78</v>
@@ -3847,7 +3851,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3693</v>
+        <v>3800</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -3888,7 +3892,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G31" t="n">
         <v>528</v>
@@ -3970,7 +3974,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G33" t="n">
         <v>258</v>
@@ -4011,7 +4015,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G34" t="n">
         <v>258</v>
@@ -4052,7 +4056,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35" t="n">
         <v>29.9</v>
@@ -4093,7 +4097,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -4175,7 +4179,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -4216,7 +4220,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G39" t="n">
         <v>55</v>
@@ -4300,7 +4304,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -4341,7 +4345,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="G42" t="n">
         <v>248</v>
@@ -4382,7 +4386,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G43" t="n">
         <v>39.9</v>
@@ -4423,7 +4427,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G44" t="n">
         <v>66</v>
@@ -4464,7 +4468,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4505,7 +4509,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,10 +501,12 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5924</v>
-      </c>
-      <c r="G2" t="n">
-        <v>138</v>
+        <v>5941</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -542,10 +544,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>561</v>
-      </c>
-      <c r="G3" t="n">
-        <v>168</v>
+        <v>563</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -583,7 +587,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1124</v>
+        <v>1151</v>
       </c>
       <c r="G4" t="n">
         <v>59</v>
@@ -624,7 +628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1067</v>
+        <v>1082</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -665,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -706,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
         <v>58</v>
@@ -788,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="G9" t="n">
         <v>89</v>
@@ -829,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -870,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -911,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -952,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2086</v>
+        <v>2120</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
@@ -993,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
@@ -1034,7 +1038,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1155</v>
+        <v>1186</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1118,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G17" t="n">
         <v>88</v>
@@ -1159,7 +1163,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="G18" t="n">
         <v>68</v>
@@ -1200,7 +1204,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1245,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G20" t="n">
         <v>79</v>
@@ -1282,7 +1286,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="G21" t="n">
         <v>78</v>
@@ -1366,7 +1370,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1409,7 +1413,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3800</v>
+        <v>3912</v>
       </c>
       <c r="G24" t="n">
         <v>75</v>
@@ -1450,7 +1454,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G25" t="n">
         <v>528</v>
@@ -1491,7 +1495,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G26" t="n">
         <v>528</v>
@@ -1532,7 +1536,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G27" t="n">
         <v>258</v>
@@ -1573,7 +1577,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G28" t="n">
         <v>258</v>
@@ -1614,7 +1618,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G29" t="n">
         <v>29.9</v>
@@ -1655,7 +1659,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="G30" t="n">
         <v>89</v>
@@ -1737,7 +1741,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -1778,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
         <v>55</v>
@@ -1819,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1862,7 +1866,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -1903,7 +1907,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="G36" t="n">
         <v>248</v>
@@ -1944,7 +1948,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G37" t="n">
         <v>39.9</v>
@@ -1985,7 +1989,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G38" t="n">
         <v>66</v>
@@ -2026,7 +2030,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -2067,7 +2071,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -2094,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,40 +2152,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>90</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2196,33 +2198,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>764</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -2232,38 +2234,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>757</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>388</v>
+        <v>180</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -2278,33 +2280,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>416</v>
       </c>
       <c r="G5" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -2314,38 +2316,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>414</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>388</v>
+        <v>90</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2355,38 +2357,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -2396,38 +2398,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.04.21 19:30-04.21 21:20</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
         </is>
       </c>
     </row>
@@ -2437,38 +2439,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.04.27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.21 19:30-04.21 21:20</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
       </c>
     </row>
@@ -2478,77 +2480,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.04.27</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>408</v>
+        <v>120</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2024.05.01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>武林路77号 文化馆小剧场</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2024.05.01 19:30-05.01 21:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>120</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
@@ -2683,35 +2644,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·【星玫Rostar×Aniidol】2nd Oneman Live - 阿诗生日SP -</t>
+          <t>杭州·第六届YH樱花动漫游戏文化节</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>同协路288号 1928创意园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 21:00</t>
+          <t>2024.02.17 10:00-02.18 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>5941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>已售罄</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80948</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jNgwYzo01705479944216.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2687,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2740,19 +2701,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5924</v>
-      </c>
-      <c r="G3" t="n">
-        <v>138</v>
+        <v>563</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
         </is>
       </c>
     </row>
@@ -2762,38 +2725,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>561</v>
+        <v>1151</v>
       </c>
       <c r="G4" t="n">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -2803,38 +2766,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1124</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2849,33 +2812,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>764</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
+        <v>388</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -2890,33 +2853,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>757</v>
+        <v>1082</v>
       </c>
       <c r="G7" t="n">
-        <v>388</v>
+        <v>65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2931,33 +2894,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1067</v>
+        <v>860</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -2967,38 +2930,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>856</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -3013,33 +2976,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>416</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -3049,38 +3012,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>414</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
-        <v>388</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -3095,33 +3058,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,33 +3099,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>626</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3177,33 +3140,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>620</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>89</v>
+        <v>158</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3213,38 +3176,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3217,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3295,38 +3258,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,33 +3304,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>2120</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3345,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3396,19 +3359,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2086</v>
+        <v>1536</v>
       </c>
       <c r="G19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3418,38 +3381,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1527</v>
+        <v>1186</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3427,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3474,23 +3437,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1155</v>
-      </c>
-      <c r="G21" t="n">
-        <v>60</v>
+        <v>306</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3505,35 +3470,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>307</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>217</v>
+      </c>
+      <c r="G22" t="n">
+        <v>88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3548,33 +3511,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>214</v>
+        <v>463</v>
       </c>
       <c r="G23" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3589,33 +3552,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3630,33 +3593,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="G25" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3671,33 +3634,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>674</v>
+        <v>249</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3712,33 +3675,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>239</v>
+        <v>1077</v>
       </c>
       <c r="G27" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3753,33 +3716,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1074</v>
-      </c>
-      <c r="G28" t="n">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3773,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3851,7 +3816,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3800</v>
+        <v>3912</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -3892,7 +3857,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G31" t="n">
         <v>528</v>
@@ -3933,7 +3898,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G32" t="n">
         <v>528</v>
@@ -3974,7 +3939,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G33" t="n">
         <v>258</v>
@@ -4015,7 +3980,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G34" t="n">
         <v>258</v>
@@ -4056,7 +4021,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G35" t="n">
         <v>29.9</v>
@@ -4097,7 +4062,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -4179,7 +4144,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -4220,7 +4185,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G39" t="n">
         <v>55</v>
@@ -4261,7 +4226,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4304,7 +4269,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -4345,7 +4310,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="G42" t="n">
         <v>248</v>
@@ -4386,7 +4351,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G43" t="n">
         <v>39.9</v>
@@ -4427,7 +4392,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G44" t="n">
         <v>66</v>
@@ -4468,7 +4433,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G45" t="n">
         <v>60</v>
@@ -4509,7 +4474,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G46" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,40 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5941</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1207</v>
+      </c>
+      <c r="G2" t="n">
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -525,40 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>563</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1105</v>
+      </c>
+      <c r="G3" t="n">
+        <v>65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -568,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1151</v>
+        <v>871</v>
       </c>
       <c r="G4" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -609,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1082</v>
+        <v>95</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>860</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -696,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>93</v>
+        <v>630</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -737,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -773,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>626</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>2180</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>1546</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -937,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2120</v>
+        <v>1218</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,38 +974,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1536</v>
-      </c>
-      <c r="G14" t="n">
-        <v>65</v>
+        <v>305</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -1024,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1186</v>
+        <v>219</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -1065,35 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>306</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>477</v>
+      </c>
+      <c r="G16" t="n">
+        <v>68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1104,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1122,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>217</v>
+        <v>709</v>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -1149,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>463</v>
+        <v>258</v>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1190,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>689</v>
+        <v>1078</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1231,33 +1227,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>249</v>
-      </c>
-      <c r="G20" t="n">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1267,38 +1265,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1077</v>
-      </c>
-      <c r="G21" t="n">
-        <v>78</v>
+        <v>527</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1308,40 +1308,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4083</v>
+      </c>
+      <c r="G22" t="n">
+        <v>75</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1351,40 +1349,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>526</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>204</v>
+      </c>
+      <c r="G23" t="n">
+        <v>528</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1409,23 +1405,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3912</v>
+        <v>140</v>
       </c>
       <c r="G24" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1435,38 +1431,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="G25" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -1481,33 +1477,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="G26" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -1517,38 +1513,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G27" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1558,38 +1554,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>176</v>
+        <v>588</v>
       </c>
       <c r="G28" t="n">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1604,33 +1600,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>29.9</v>
+        <v>99</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -1640,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>566</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1681,38 +1677,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1723,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1741,19 +1737,21 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>57</v>
-      </c>
-      <c r="G32" t="n">
-        <v>70</v>
+        <v>233</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1763,38 +1761,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>351</v>
       </c>
       <c r="G33" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,40 +1802,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>230</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>912</v>
+      </c>
+      <c r="G34" t="n">
+        <v>248</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1848,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1866,19 +1862,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>338</v>
+        <v>116</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -1888,38 +1884,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>878</v>
+        <v>85</v>
       </c>
       <c r="G36" t="n">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -1929,38 +1925,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 09:00-04.20 22:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G37" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
         </is>
       </c>
     </row>
@@ -1970,118 +1966,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="G38" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>95</v>
-      </c>
-      <c r="G39" t="n">
-        <v>60</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024.04.20</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>黄姑山路51-4号 0101park</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>97</v>
-      </c>
-      <c r="G40" t="n">
-        <v>68</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2212,7 +2126,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="G3" t="n">
         <v>388</v>
@@ -2417,7 +2331,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2458,7 +2372,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>408</v>
@@ -2585,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2639,40 +2553,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花动漫游戏文化节</t>
+          <t>杭州·美哉美物 动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>新街街道通城路598号 粮仓艺术公园</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.23 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5941</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1207</v>
+      </c>
+      <c r="G2" t="n">
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/cYpLgik81703819171170.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
         </is>
       </c>
     </row>
@@ -2682,40 +2594,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州·第六届YH樱花漫展-SVIP嘉宾前排票</t>
+          <t>杭州·《卡农》永恒经典名曲音乐会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.18 17:00</t>
+          <t>2024.02.24 19:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>563</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/kXKTau2B1705650353850.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
         </is>
       </c>
     </row>
@@ -2725,38 +2635,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.23</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州·美哉美物 动漫游戏嘉年华</t>
+          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新街街道通城路598号 粮仓艺术公园</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.23 10:00-02.24 17:00</t>
+          <t>2024.02.24 19:30-02.24 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1151</v>
+        <v>771</v>
       </c>
       <c r="G4" t="n">
-        <v>59</v>
+        <v>388</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81393</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/nXpdoSAk1706154911514.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
         </is>
       </c>
     </row>
@@ -2771,33 +2681,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州·《卡农》永恒经典名曲音乐会</t>
+          <t>杭州·次元幻想动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>武林路77号 浙江省文化馆小剧场（原群艺馆小剧场）</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1105</v>
       </c>
       <c r="G5" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80904</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/56p4IV4Q1705396799583.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
         </is>
       </c>
     </row>
@@ -2812,33 +2722,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州·才八点派对 Day1 </t>
+          <t>杭州第35届 中二病 原神x星穹only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>康候圣街99号 顺丰创新中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 19:30-02.24 22:00</t>
+          <t>2024.02.24 11:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>764</v>
+        <v>871</v>
       </c>
       <c r="G6" t="n">
-        <v>388</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81692</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/TXDC8NrV1706866356112.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
         </is>
       </c>
     </row>
@@ -2848,38 +2758,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·次元幻想动漫游戏嘉年华</t>
+          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>杭州市江干区新业路39号 杭州大剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.25 19:30-02.25 21:10</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1082</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80425</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ZlI1Z4Xh1704266621625.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
         </is>
       </c>
     </row>
@@ -2889,38 +2799,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.02.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州第35届 中二病 原神x星穹only</t>
+          <t>杭州·才八点派对 Day2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>康候圣街99号 顺丰创新中心</t>
+          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.24 17:00</t>
+          <t>2024.02.25 19:30-02.25 22:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>860</v>
+        <v>416</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>388</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79890</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/HMGhhQPS1702884424386.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
         </is>
       </c>
     </row>
@@ -2930,38 +2840,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州·大船文化·终极无伴奏——宁峰演绎伊萨伊与帕格尼尼音乐会</t>
+          <t>杭州· young comic漾动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杭州市江干区新业路39号 杭州大剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 21:10</t>
+          <t>2024.03.02 09:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81311</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/k53cbfSX1706006394089.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
         </is>
       </c>
     </row>
@@ -2971,38 +2881,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.25</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>杭州·才八点派对 Day2</t>
+          <t>杭州·亚米二次茶话会展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>通货路918号粮仓艺术公园7号楼 SoFunLivehouse</t>
+          <t>湖州街20号 纳德自由酒店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.25 19:30-02.25 22:00</t>
+          <t>2024.03.02 13:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>416</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>388</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81696</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XaTpvowc1706867543851.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
         </is>
       </c>
     </row>
@@ -3017,33 +2927,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>杭州· young comic漾动漫嘉年华</t>
+          <t>杭州·杭州灵能百分百only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>水博大道118号 宝盛水博园大酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 09:00-03.02 17:00</t>
+          <t>2024.03.02 09:30-03.02 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>630</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81117</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Y7hnq4gB1706517272632.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
         </is>
       </c>
     </row>
@@ -3058,33 +2968,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>杭州·亚米二次茶话会展</t>
+          <t>杭州·次元幻想--二次元全女夜场</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>湖州街20号 纳德自由酒店</t>
+          <t>保淑路2号 The Queen皇后</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81702</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
         </is>
       </c>
     </row>
@@ -3094,38 +3004,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>杭州·杭州灵能百分百only</t>
+          <t>杭州·Comics Market同人展·不问归期</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>水博大道118号 宝盛水博园大酒店</t>
+          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.02 09:30-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>626</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80099</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/O6Gy2Re21704184555408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3135,38 +3045,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·次元幻想--二次元全女夜场</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>保淑路2号 The Queen皇后</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 19:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81808</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sUUtSPh91707295826425.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3176,38 +3086,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>杭州·Comics Market同人展·不问归期</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>九堡街道九环路7号 桔子酒店九堡客运站店</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81564</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/ACyAOLPy1706685013593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3217,38 +3127,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>2180</v>
       </c>
       <c r="G16" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3263,33 +3173,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>1546</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3299,38 +3209,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2120</v>
+        <v>1218</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3340,38 +3250,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1536</v>
-      </c>
-      <c r="G19" t="n">
-        <v>65</v>
+        <v>305</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3386,33 +3298,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1186</v>
+        <v>219</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3427,35 +3339,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>306</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>477</v>
+      </c>
+      <c r="G21" t="n">
+        <v>68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3470,33 +3380,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -3511,33 +3421,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·排球少年*蓝锁ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>463</v>
+        <v>709</v>
       </c>
       <c r="G23" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
         </is>
       </c>
     </row>
@@ -3552,33 +3462,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="G24" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -3593,33 +3503,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>亚太路湘湖3期东南侧约290米 原创壹号羽毛球馆</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>689</v>
+        <v>1078</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81075</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9AL6kYuj1705634962275.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -3634,33 +3544,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>249</v>
-      </c>
-      <c r="G26" t="n">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -3670,38 +3582,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1077</v>
-      </c>
-      <c r="G27" t="n">
-        <v>78</v>
+        <v>527</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3711,40 +3625,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4083</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -3754,40 +3666,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>526</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>204</v>
+      </c>
+      <c r="G29" t="n">
+        <v>528</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3707,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3812,23 +3722,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3912</v>
+        <v>140</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -3838,38 +3748,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="G31" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -3884,33 +3794,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="G32" t="n">
-        <v>528</v>
+        <v>258</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -3920,38 +3830,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G33" t="n">
-        <v>258</v>
+        <v>29.9</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -3961,38 +3871,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>176</v>
+        <v>588</v>
       </c>
       <c r="G34" t="n">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -4007,33 +3917,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
-        <v>29.9</v>
+        <v>99</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
         </is>
       </c>
     </row>
@@ -4043,38 +3953,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>566</v>
+        <v>58</v>
       </c>
       <c r="G36" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -4084,38 +3994,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4040,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4144,19 +4054,21 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>57</v>
-      </c>
-      <c r="G38" t="n">
-        <v>70</v>
+        <v>233</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -4166,38 +4078,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>28</v>
+        <v>351</v>
       </c>
       <c r="G39" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4207,40 +4119,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>230</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>912</v>
+      </c>
+      <c r="G40" t="n">
+        <v>248</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4165,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4269,19 +4179,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>338</v>
+        <v>116</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
         </is>
       </c>
     </row>
@@ -4291,38 +4201,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·赛马娘only—晴空雏菊</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.13 09:00-04.13 18:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>878</v>
+        <v>85</v>
       </c>
       <c r="G42" t="n">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
         </is>
       </c>
     </row>
@@ -4332,38 +4242,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.20 09:00-04.20 22:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G43" t="n">
-        <v>39.9</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
         </is>
       </c>
     </row>
@@ -4373,38 +4283,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="G44" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
       </c>
     </row>
@@ -4414,38 +4324,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
+          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
+          <t>2024.04.21 19:30-04.21 21:20</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4455,38 +4365,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>杭州·白日梦次元动漫嘉年华</t>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>黄姑山路51-4号 0101park</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.20 10:00-04.21 18:00</t>
+          <t>2024.04.27 19:30-04.27 21:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>68</v>
+        <v>408</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
         </is>
       </c>
     </row>
@@ -4496,118 +4406,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
+          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
+          <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.21 19:30-04.21 21:20</t>
+          <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024.04.27</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>13</v>
-      </c>
-      <c r="G48" t="n">
-        <v>408</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024.05.01</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>武林路77号 文化馆小剧场</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.05.01 19:30-05.01 21:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>5</v>
-      </c>
-      <c r="G49" t="n">
-        <v>120</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1207</v>
+        <v>1230</v>
       </c>
       <c r="G2" t="n">
         <v>59</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1105</v>
+        <v>1122</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G7" t="n">
         <v>89</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2180</v>
+        <v>2223</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1218</v>
+        <v>1240</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G15" t="n">
         <v>88</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G18" t="n">
         <v>79</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G19" t="n">
         <v>78</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4083</v>
+        <v>4194</v>
       </c>
       <c r="G22" t="n">
         <v>75</v>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G24" t="n">
         <v>528</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G25" t="n">
         <v>258</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G26" t="n">
         <v>258</v>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G27" t="n">
         <v>29.9</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="G28" t="n">
         <v>89</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
         <v>99</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
         <v>70</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" t="n">
         <v>55</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="G34" t="n">
         <v>248</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G35" t="n">
         <v>39.9</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G36" t="n">
         <v>66</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G38" t="n">
         <v>68</v>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="G3" t="n">
         <v>388</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G5" t="n">
         <v>388</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1207</v>
+        <v>1230</v>
       </c>
       <c r="G2" t="n">
         <v>59</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1105</v>
+        <v>1122</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G8" t="n">
         <v>388</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G11" t="n">
         <v>89</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G12" t="n">
         <v>158</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2180</v>
+        <v>2223</v>
       </c>
       <c r="G16" t="n">
         <v>70</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1218</v>
+        <v>1240</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G20" t="n">
         <v>88</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G21" t="n">
         <v>68</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="G24" t="n">
         <v>79</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4083</v>
+        <v>4194</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G30" t="n">
         <v>528</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G31" t="n">
         <v>258</v>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G32" t="n">
         <v>258</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G33" t="n">
         <v>29.9</v>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
         <v>99</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="G40" t="n">
         <v>248</v>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G41" t="n">
         <v>39.9</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G42" t="n">
         <v>66</v>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G43" t="n">
         <v>60</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>

--- a/杭州-漫展信息.xlsx
+++ b/杭州-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1230</v>
+        <v>1252</v>
       </c>
       <c r="G2" t="n">
         <v>59</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1122</v>
+        <v>1147</v>
       </c>
       <c r="G3" t="n">
         <v>65</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="G4" t="n">
         <v>50</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
         <v>58</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/uPDIsIoV1708311822716.jpeg</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="G7" t="n">
         <v>89</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
         <v>50</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2223</v>
+        <v>2267</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1240</v>
+        <v>1285</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G15" t="n">
         <v>88</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="G16" t="n">
         <v>68</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1145,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·百鬼夜行·咒术回战only</t>
+          <t>杭州·春和景明代号鸢only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长生路18号 梅地亚宾馆</t>
+          <t>金沙大道681号 金沙湖大剧院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.16 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>265</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81894</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1RX6wnFN1708323470900.png</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·第十届次元鹿角动漫游戏展</t>
+          <t>杭州·百鬼夜行·咒术回战only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
+          <t>长生路18号 梅地亚宾馆</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1080</v>
+        <v>272</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81478</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/4weHdCdk1706495040356.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,35 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
+          <t>杭州·第十届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>大岭山路156号 爱丽芬城堡</t>
+          <t>万融城3幢1楼 头号玩家数字运动俱乐部</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1083</v>
+      </c>
+      <c r="G20" t="n">
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81136</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w8iHjfOA1705651976885.jpeg</t>
         </is>
       </c>
     </row>
@@ -1265,40 +1263,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
+          <t>杭州·筑梦城堡巡回展降临之章（取消）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>大岭山路156号 爱丽芬城堡</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.17 12:30-03.17 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>527</v>
+        <v>17</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81217</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/oEILAgir1705908585941.png</t>
         </is>
       </c>
     </row>
@@ -1308,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展</t>
+          <t>杭州·造梦探险家——次元茶话会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>临平街道北沙西路156-1号 杭州临平遇上设计师酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4194</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81914</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/R5EvMIO01708335487215.png</t>
         </is>
       </c>
     </row>
@@ -1349,38 +1347,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
+          <t>杭州·ComicMe动漫嘉年华 · 马正阳专场</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.17 12:30-03.17 16:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>204</v>
-      </c>
-      <c r="G23" t="n">
-        <v>528</v>
+        <v>527</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81375</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/rNzSh0nq1706149891822.jpeg</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展  岩永彻也内场票</t>
+          <t>杭州·AD02动漫展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,23 +1405,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.24 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>143</v>
+        <v>4369</v>
       </c>
       <c r="G24" t="n">
-        <v>528</v>
+        <v>75</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80905</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/D3QaPamg1705397424553.jpeg</t>
         </is>
       </c>
     </row>
@@ -1431,38 +1431,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
+          <t>杭州·AD02动漫展  青柳尊哉内场票</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.24 12:00-03.24 16:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="G25" t="n">
-        <v>258</v>
+        <v>528</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81503</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OmqxboDC1706522627528.jpeg</t>
         </is>
       </c>
     </row>
@@ -1472,38 +1472,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
+          <t>杭州·现世繁华-代号鸢only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>石祥路575号 杭州海外海纳川大酒店(万达广场渡驾桥地铁站店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.24 09:30-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>186</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>258</v>
+        <v>76</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81905</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/m3upuV2F1708327958926.jpeg</t>
         </is>
       </c>
     </row>
@@ -1513,38 +1513,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>杭州·Look Look动漫嘉年华</t>
+          <t>杭州·AD02动漫展  岩永彻也内场票</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
+          <t>浙江省杭州市萧山区奔竞大道353号 国际博览中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:30</t>
+          <t>2024.03.24 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="G27" t="n">
-        <v>29.9</v>
+        <v>528</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81239</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hww9WUpD1705914756383.jpeg</t>
         </is>
       </c>
     </row>
@@ -1554,38 +1554,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杭州·排球少年only·春日校庆</t>
+          <t>杭州·AD02动漫展--亦之紫F、L句号内场票</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>之江路149号 云栖培训基地</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 12:00-03.24 16:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>602</v>
+        <v>123</v>
       </c>
       <c r="G28" t="n">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81836</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ecrRfQce1707375167618.jpeg</t>
         </is>
       </c>
     </row>
@@ -1595,38 +1595,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杭州·第十一届次元鹿角动漫游戏展</t>
+          <t>杭州·AD02动漫展--钟晨瑶内场票</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.24 09:30-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="G29" t="n">
-        <v>99</v>
+        <v>258</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81820</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ChHZGPj81706867261395.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/aHRmCxr31707296105225.jpeg</t>
         </is>
       </c>
     </row>
@@ -1636,38 +1636,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杭州·创造力动漫游戏嘉年华1.0</t>
+          <t>杭州·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>聚业路27号电魂大厦B座1楼 电魂自在里文化空间(硅谷书房)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G30" t="n">
-        <v>70</v>
+        <v>29.9</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81757</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/anrpU73c1707106069934.jpeg</t>
         </is>
       </c>
     </row>
@@ -1677,38 +1677,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杭州·梦漫星河动漫展</t>
+          <t>杭州·二次元拾梦漫展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>转塘街道创意路1号 艺创小镇凤凰创意大厦</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 18:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81902</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/OfonGbvl1708325977132.jpeg</t>
         </is>
       </c>
     </row>
@@ -1718,40 +1718,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>杭州·第九届萌次元动漫嘉年华</t>
+          <t>杭州·排球少年only·春日校庆</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
+          <t>之江路149号 云栖培训基地</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 10:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>234</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>629</v>
+      </c>
+      <c r="G32" t="n">
+        <v>89</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81511</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/qJrJxGUy1706581833764.jpeg</t>
         </is>
       </c>
     </row>
@@ -1761,38 +1759,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
+          <t>杭州·第十一届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>富春路80号(甬江路地铁站A口旁) 杭州全民健身中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>355</v>
+        <v>24</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81694</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/y2UW01sH1708324524472.jpeg</t>
         </is>
       </c>
     </row>
@@ -1802,38 +1800,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+          <t>杭州·创造力动漫游戏嘉年华1.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>921</v>
+        <v>62</v>
       </c>
       <c r="G34" t="n">
-        <v>248</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81078</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/o4cl1vwE1705635692432.jpeg</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1841,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.04.05</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+          <t>杭州·梦漫星河动漫展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.05 09:30-04.05 16:30</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="G35" t="n">
-        <v>39.9</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81699</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/sZfZd47Y1706868453434.jpeg</t>
         </is>
       </c>
     </row>
@@ -1884,38 +1882,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>杭州·赛马娘only—晴空雏菊</t>
+          <t>杭州·第九届萌次元动漫嘉年华</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+          <t>长乐路29号五组2幢 杭州运河文化发布中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.13 09:00-04.13 18:00</t>
+          <t>2024.04.04 10:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>86</v>
-      </c>
-      <c r="G36" t="n">
-        <v>66</v>
+        <v>234</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78866</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/8jSeAOZH1700636327971.jpeg</t>
         </is>
       </c>
     </row>
@@ -1925,38 +1925,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>杭州·SK怀旧展&amp;偶像专场</t>
+          <t>杭州·2024ESCC游戏电竞博览会暨新次元微光青春动漫交流会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.20 22:00</t>
+          <t>2024.04.05 09:30-04.05 16:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>112</v>
+        <v>360</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81450</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/49hIEgVb1706252734479.jpeg</t>
         </is>
       </c>
     </row>
@@ -1966,36 +1966,200 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024.04.05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>杭州·ESCC电竞博览会 倒霉死勒内场票</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>938</v>
+      </c>
+      <c r="G38" t="n">
+        <v>248</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81681</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/suXI547M1706862164353.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024.04.05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>杭州·ESCC电竞博览会·钱琛签售礼包</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>钱江世纪城奔竞大道353号 杭州国际博览中心</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.04.05 09:30-04.05 16:30</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>120</v>
+      </c>
+      <c r="G39" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81680</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/noqtqw701706861615316.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024.04.13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>杭州·赛马娘only—晴空雏菊</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>北干街道萧杭路689号 时尚外滩艺术中心</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.13 09:00-04.13 18:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>88</v>
+      </c>
+      <c r="G40" t="n">
+        <v>66</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81767</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ViMb8nbw1707122090281.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2024.04.20</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>杭州·SK怀旧展&amp;偶像专场</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.04.20 09:00-04.20 22:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>120</v>
+      </c>
+      <c r="G41" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81764</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/mtdbSuTZ1707119415384.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024.04.20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>杭州·白日梦次元动漫嘉年华</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>黄姑山路51-4号 0101park</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2024.04.20 10:00-04.21 18:00</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>104</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F42" t="n">
+        <v>107</v>
+      </c>
+      <c r="G42" t="n">
         <v>68</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81634</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/n65ZLevi1706777788165.jpeg</t>
         </is>
@@ -2012,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2085,7 +2249,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>90</v>
@@ -2126,7 +2290,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="G3" t="n">
         <v>388</v>
@@ -2208,7 +2372,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G5" t="n">
         <v>388</v>
@@ -2230,38 +2394,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·壹起ACG·次元拼盘Live</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>金沙大道盈都吾角广场 ECHO SPACE(龙湖杭州吾角天街)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.03 13:00-03.03 19:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81903</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0P0TOwv51708326773542.jpeg</t>
         </is>
       </c>
     </row>
@@ -2271,38 +2435,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2312,38 +2476,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.04.21</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
+          <t>湖墅南路136-138号 浙话艺术剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.04.21 19:30-04.21 21:20</t>
+          <t>2024.03.16 19:00-03.16 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>380</v>
+        <v>72</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,38 +2517,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.04.27</t>
+          <t>2024.04.21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>杭州·大船文化·迪士尼奇妙庆典演唱会 Disney in Concert A Magical Celebration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>金沙大道681号 金沙湖大剧院</t>
+          <t>杭州市西湖区省府路9号 浙江省人民大会堂</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.04.27 19:30-04.27 21:30</t>
+          <t>2024.04.21 19:30-04.21 21:20</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>408</v>
+        <v>380</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81832</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/SAhUi36h1707359425502.jpeg</t>
         </is>
       </c>
     </row>
@@ -2394,36 +2558,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024.04.27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>杭州· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>金沙大道681号 金沙湖大剧院</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.04.27 19:30-04.27 21:30</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>408</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80936</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/qqwyEQLF1705476706621.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>2024.05.01</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>杭州·英文原版话剧《一个人的莎士比亚》</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>武林路77号 文化馆小剧场</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2024.05.01 19:30-05.01 21:00</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>5</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>120</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81559</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/4q2shrPd1706682353362.jpeg</t>
         </is>
@@ -2499,7 +2704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2572,7 +2777,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1230</v>
+        <v>1252</v>
       </c>
       <c r="G2" t="n">
         <v>59</v>
@@ -2613,7 +2818,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>90</v>
@@ -2654,7 +2859,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="G4" t="n">
         <v>388</v>
@@ -2695,7 +2900,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1122</v>
+        <v>1147</v>
       </c>
       <c r="G5" t="n">
         <v>65</v>
@@ -2736,7 +2941,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="G6" t="n">
         <v>50</v>
@@ -2818,7 +3023,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G8" t="n">
         <v>388</v>
@@ -2859,7 +3064,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -2900,7 +3105,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
         <v>58</v>
@@ -2912,7 +3117,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/IWtNSAXt1707014699653.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/uPDIsIoV1708311822716.jpeg</t>
         </is>
       </c>
     </row>
@@ -2941,7 +3146,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="G11" t="n">
         <v>89</v>
@@ -2982,7 +3187,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
         <v>158</v>
@@ -3023,7 +3228,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -3045,38 +3250,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.08</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
+          <t>杭州·壹起ACG·次元拼盘Live</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>曙光路31号 浙江音乐厅</t>
+          <t>金沙大道盈都吾角广场 ECHO SPACE(龙湖杭州吾角天街)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.08 19:30-03.08 21:00</t>
+          <t>2024.03.03 13:00-03.03 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81903</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0P0TOwv51708326773542.jpeg</t>
         </is>
       </c>
     </row>
@@ -3086,38 +3291,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>建德·星之漫游戏嘉年华</t>
+          <t>杭州·《LALALAND爱乐之城》浪漫主题音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>桥东路一号1号 皇爵君廷大酒店</t>
+          <t>曙光路31号 浙江音乐厅</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 17:00</t>
+          <t>2024.03.08 19:30-03.08 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81554</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/VpdygwNH1706681692568.jpeg</t>
         </is>
       </c>
     </row>
@@ -3132,33 +3337,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
+          <t>建德·星之漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
+          <t>桥东路一号1号 皇爵君廷大酒店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2223</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80666</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/BWYzYuBW1705030650858.jpeg</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3378,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>杭州·异次结界动漫嘉年华</t>
+          <t>杭州·COMIC TIME动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>德胜东路2539号 梦马汽车小镇</t>
+          <t>沈半路171号 T-Car杭州汽车文化主题公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3187,19 +3392,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1552</v>
+        <v>2267</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81211</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7JXZatUK1707187527932.jpeg</t>
         </is>
       </c>
     </row>
@@ -3209,38 +3414,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华</t>
+          <t>杭州·异次结界动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长江南路336号 白马湖国际会展中心</t>
+          <t>德胜东路2539号 梦马汽车小镇</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1240</v>
+        <v>1564</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79935</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/9abgpzRQ1704452704753.jpeg</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3460,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
+          <t>杭州·ComicMe动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3265,25 +3470,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 12:30-03.16 16:30</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>305</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1285</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81214</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/iN5DafVM1705907838033.jpeg</t>
         </is>
       </c>
     </row>
@@ -3298,33 +3501,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>杭州·OZ·富坚义博only</t>
+          <t>杭州·ComicMe动漫嘉年华 · 胡良伟专场</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
+          <t>长江南路336号 白马湖国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 12:30-03.16 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>222</v>
-      </c>
-      <c r="G20" t="n">
-        <v>88</v>
+        <v>305</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81382</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4UJgRWeM1706151833915.jpeg</t>
         </is>
       </c>
     </row>
@@ -3339,33 +3544,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>杭州·SST动漫嘉年华</t>
+          <t>杭州·OZ·富坚义博only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>沈半路171号 Tcar汽车文化主题公园</t>
+          <t>北干街道萧杭路689号浙农东巢艺术公园 Fashion Bund时尚外滩艺术中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>487</v>
+        <v>226</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81151</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/CxqdeAPa1705658329588.jpeg</t>
         </is>
       </c>
     </row>
@@ -3380,33 +3585,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>杭州·SST动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>湖墅南路136-138号 浙话艺术剧院</t>
+          <t>沈半路171号 Tcar汽车文化主题公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 21:00</t>
+          <t>2024.03.16 09:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="G22" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81557</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NXR7ATah1706682091721.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/yFyT2uAT1705897787652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3421,33 +3626,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杭州·排球少年*蓝锁ONLY</t>
+          <t>杭州·《挪威的森林》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-